--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A82F3FD-0BE8-47D8-9579-FBD63B355AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B434F2-937F-4D97-A920-864AD24D7C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1240,7 +1240,7 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1459,73 +1459,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1555,6 +1488,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1604,9 +1540,74 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1624,18 +1625,6 @@
           <bgColor theme="4" tint="0.79979857783745845"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1660,6 +1649,18 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8412,169 +8413,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8724,16 +8562,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8753,7 +8591,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8870,6 +8708,169 @@
   <dataFields count="2">
     <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9106,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81" t="s">
+      <c r="C4" s="123"/>
+      <c r="D4" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81" t="s">
+      <c r="E4" s="123"/>
+      <c r="F4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81" t="s">
+      <c r="G4" s="123"/>
+      <c r="H4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="81"/>
-      <c r="J4" s="82" t="s">
+      <c r="I4" s="123"/>
+      <c r="J4" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="83"/>
-      <c r="L4" s="84"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="126"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="86">
+      <c r="B5" s="114">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="87">
+      <c r="C5" s="114"/>
+      <c r="D5" s="115">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="88">
+      <c r="E5" s="115"/>
+      <c r="F5" s="116">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="88"/>
-      <c r="H5" s="89">
+      <c r="G5" s="116"/>
+      <c r="H5" s="117">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="89"/>
-      <c r="J5" s="76">
+      <c r="I5" s="117"/>
+      <c r="J5" s="118">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="77"/>
-      <c r="L5" s="78"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="120"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="85">
+      <c r="B6" s="113">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85">
+      <c r="C6" s="113"/>
+      <c r="D6" s="113">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85">
+      <c r="E6" s="113"/>
+      <c r="F6" s="113">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85">
+      <c r="G6" s="113"/>
+      <c r="H6" s="113">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="85"/>
-      <c r="J6" s="101">
+      <c r="I6" s="113"/>
+      <c r="J6" s="76">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="102"/>
-      <c r="L6" s="103"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="78"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91" t="s">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="91"/>
-      <c r="F7" s="92" t="s">
+      <c r="E7" s="103"/>
+      <c r="F7" s="104" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91" t="s">
+      <c r="G7" s="103"/>
+      <c r="H7" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="91"/>
-      <c r="J7" s="104" t="s">
+      <c r="I7" s="103"/>
+      <c r="J7" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="81"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="108"/>
-      <c r="L8" s="109"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="83"/>
+      <c r="L8" s="84"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="114"/>
-      <c r="M10" s="114"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="114"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="90"/>
+      <c r="N10" s="90"/>
+      <c r="O10" s="90"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="126"/>
-      <c r="C11" s="97" t="s">
+      <c r="B11" s="102"/>
+      <c r="C11" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98" t="s">
+      <c r="D11" s="109"/>
+      <c r="E11" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="98"/>
-      <c r="G11" s="99" t="s">
+      <c r="F11" s="110"/>
+      <c r="G11" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="99"/>
-      <c r="I11" s="100" t="s">
+      <c r="H11" s="111"/>
+      <c r="I11" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="100"/>
+      <c r="J11" s="112"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="90" t="s">
+      <c r="L11" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="90"/>
-      <c r="N11" s="112" t="s">
+      <c r="M11" s="86"/>
+      <c r="N11" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="112"/>
+      <c r="O11" s="88"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="126"/>
+      <c r="B12" s="102"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10356,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="115" t="s">
+      <c r="B33" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="115"/>
-      <c r="D33" s="115"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="114" t="s">
+      <c r="F33" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="114"/>
-      <c r="H33" s="114"/>
-      <c r="I33" s="114"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="114"/>
-      <c r="L33" s="114"/>
-      <c r="M33" s="114"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="90"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10386,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="90" t="s">
+      <c r="G34" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="111"/>
-      <c r="I34" s="112" t="s">
+      <c r="H34" s="87"/>
+      <c r="I34" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="113"/>
-      <c r="K34" s="124" t="s">
+      <c r="J34" s="89"/>
+      <c r="K34" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="125"/>
-      <c r="M34" s="125"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="101"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10426,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="116" t="s">
+      <c r="K35" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="117"/>
+      <c r="L35" s="93"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10465,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="118">
+      <c r="K36" s="94">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="119"/>
+      <c r="L36" s="95"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10506,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="120">
+      <c r="K37" s="96">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="121"/>
+      <c r="L37" s="97"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10547,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="122">
+      <c r="K38" s="98">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="123"/>
+      <c r="L38" s="99"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10695,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="110" t="s">
+      <c r="B50" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
-      <c r="D50" s="110"/>
+      <c r="C50" s="85"/>
+      <c r="D50" s="85"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10777,6 +10778,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10793,34 +10822,6 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17901,8 +17902,8 @@
       <c r="A2" t="s">
         <v>201</v>
       </c>
-      <c r="B2">
-        <v>3</v>
+      <c r="B2" s="128">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B434F2-937F-4D97-A920-864AD24D7C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EF8D41-26F4-4E08-82F1-D6C1E8A869B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1459,6 +1459,74 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1488,9 +1556,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1540,74 +1605,9 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1639,7 +1639,16 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1651,16 +1660,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8413,6 +8413,317 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="4">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8560,317 +8871,6 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="8">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="122"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123" t="s">
+      <c r="C4" s="82"/>
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="123"/>
-      <c r="J4" s="124" t="s">
+      <c r="I4" s="82"/>
+      <c r="J4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="125"/>
-      <c r="L4" s="126"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="114">
+      <c r="B5" s="87">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="115">
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="115"/>
-      <c r="F5" s="116">
+      <c r="E5" s="88"/>
+      <c r="F5" s="89">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="116"/>
-      <c r="H5" s="117">
+      <c r="G5" s="89"/>
+      <c r="H5" s="90">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="117"/>
-      <c r="J5" s="118">
+      <c r="I5" s="90"/>
+      <c r="J5" s="77">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="119"/>
-      <c r="L5" s="120"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="79"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="113">
+      <c r="B6" s="86">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="113"/>
-      <c r="D6" s="113">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="113"/>
-      <c r="F6" s="113">
+      <c r="E6" s="86"/>
+      <c r="F6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="113"/>
-      <c r="H6" s="113">
+      <c r="G6" s="86"/>
+      <c r="H6" s="86">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="113"/>
-      <c r="J6" s="76">
+      <c r="I6" s="86"/>
+      <c r="J6" s="102">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="77"/>
-      <c r="L6" s="78"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="104"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="103"/>
-      <c r="F7" s="104" t="s">
+      <c r="E7" s="92"/>
+      <c r="F7" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="103"/>
-      <c r="J7" s="79" t="s">
+      <c r="I7" s="92"/>
+      <c r="J7" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="80"/>
-      <c r="L7" s="81"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="107"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="105"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="84"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="110"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="90"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="O10" s="90"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="115"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="102"/>
-      <c r="C11" s="109" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="109"/>
-      <c r="E11" s="110" t="s">
+      <c r="D11" s="98"/>
+      <c r="E11" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="110"/>
-      <c r="G11" s="111" t="s">
+      <c r="F11" s="99"/>
+      <c r="G11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="111"/>
-      <c r="I11" s="112" t="s">
+      <c r="H11" s="100"/>
+      <c r="I11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="112"/>
+      <c r="J11" s="101"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="86" t="s">
+      <c r="L11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="86"/>
-      <c r="N11" s="88" t="s">
+      <c r="M11" s="91"/>
+      <c r="N11" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="88"/>
+      <c r="O11" s="113"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="102"/>
+      <c r="B12" s="127"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10357,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="90" t="s">
+      <c r="F33" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="90"/>
-      <c r="H33" s="90"/>
-      <c r="I33" s="90"/>
-      <c r="J33" s="90"/>
-      <c r="K33" s="90"/>
-      <c r="L33" s="90"/>
-      <c r="M33" s="90"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="115"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="115"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="86" t="s">
+      <c r="G34" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="87"/>
-      <c r="I34" s="88" t="s">
+      <c r="H34" s="112"/>
+      <c r="I34" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="89"/>
-      <c r="K34" s="100" t="s">
+      <c r="J34" s="114"/>
+      <c r="K34" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="101"/>
-      <c r="M34" s="101"/>
+      <c r="L34" s="126"/>
+      <c r="M34" s="126"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="92" t="s">
+      <c r="K35" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="93"/>
+      <c r="L35" s="118"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10466,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="94">
+      <c r="K36" s="119">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="95"/>
+      <c r="L36" s="120"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10507,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="96">
+      <c r="K37" s="121">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="97"/>
+      <c r="L37" s="122"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10548,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="98">
+      <c r="K38" s="123">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="99"/>
+      <c r="L38" s="124"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10696,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10778,34 +10778,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10822,6 +10794,34 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17196,21 +17196,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="128" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="E1" s="127" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="E1" s="128" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="I1" s="127" t="s">
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="I1" s="128" t="s">
         <v>160</v>
       </c>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="59" t="s">
@@ -17902,8 +17902,8 @@
       <c r="A2" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="128">
-        <v>3.1</v>
+      <c r="B2" s="76">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EF8D41-26F4-4E08-82F1-D6C1E8A869B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B7B04F-30D1-475F-82E4-6B8EC78EED98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17894,8 +17894,8 @@
         <v>200</v>
       </c>
       <c r="B1" s="75">
-        <f ca="1">+TODAY()</f>
-        <v>46189</v>
+        <f ca="1">+TODAY()+1</f>
+        <v>46190</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B7B04F-30D1-475F-82E4-6B8EC78EED98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E272C094-5167-4117-96F8-A7E9EE3E43A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1460,73 +1460,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1556,6 +1489,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1605,6 +1541,70 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1627,7 +1627,16 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1639,16 +1648,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -8413,154 +8413,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
@@ -8694,16 +8546,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8723,7 +8575,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8871,6 +8723,154 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="122" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82" t="s">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="124"/>
+      <c r="F4" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82" t="s">
+      <c r="G4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="87">
+      <c r="B5" s="115">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88">
+      <c r="C5" s="115"/>
+      <c r="D5" s="116">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="89">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="89"/>
-      <c r="H5" s="90">
+      <c r="G5" s="117"/>
+      <c r="H5" s="118">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="77">
+      <c r="I5" s="118"/>
+      <c r="J5" s="119">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="79"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="86">
+      <c r="B6" s="114">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86">
+      <c r="C6" s="114"/>
+      <c r="D6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86">
+      <c r="E6" s="114"/>
+      <c r="F6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86">
+      <c r="G6" s="114"/>
+      <c r="H6" s="114">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="102">
+      <c r="I6" s="114"/>
+      <c r="J6" s="77">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="103"/>
-      <c r="L6" s="104"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="105" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="80" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="110"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="115"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="127"/>
-      <c r="C11" s="98" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="99" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="100" t="s">
+      <c r="F11" s="111"/>
+      <c r="G11" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="101" t="s">
+      <c r="H11" s="112"/>
+      <c r="I11" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="101"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="91" t="s">
+      <c r="L11" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="91"/>
-      <c r="N11" s="113" t="s">
+      <c r="M11" s="87"/>
+      <c r="N11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="113"/>
+      <c r="O11" s="89"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="127"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10357,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="115" t="s">
+      <c r="F33" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="91" t="s">
+      <c r="G34" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="112"/>
-      <c r="I34" s="113" t="s">
+      <c r="H34" s="88"/>
+      <c r="I34" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="114"/>
-      <c r="K34" s="125" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="117" t="s">
+      <c r="K35" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="118"/>
+      <c r="L35" s="94"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10466,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="119">
+      <c r="K36" s="95">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="120"/>
+      <c r="L36" s="96"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10507,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K37" s="97">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="122"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10548,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="123">
+      <c r="K38" s="99">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="124"/>
+      <c r="L38" s="100"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10696,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="111" t="s">
+      <c r="B50" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10778,6 +10778,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10794,34 +10822,6 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17894,7 +17894,6 @@
         <v>200</v>
       </c>
       <c r="B1" s="75">
-        <f ca="1">+TODAY()+1</f>
         <v>46190</v>
       </c>
     </row>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E272C094-5167-4117-96F8-A7E9EE3E43A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854BE393-4CB5-4A9C-B6EC-CFE1714BE6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1460,6 +1460,73 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1489,9 +1556,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1541,70 +1605,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1625,18 +1625,6 @@
           <bgColor theme="4" tint="0.79979857783745845"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1661,6 +1649,18 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8413,169 +8413,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8725,16 +8562,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8754,7 +8591,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8871,6 +8708,169 @@
   <dataFields count="2">
     <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124" t="s">
+      <c r="C4" s="82"/>
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="124"/>
-      <c r="J4" s="125" t="s">
+      <c r="I4" s="82"/>
+      <c r="J4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="126"/>
-      <c r="L4" s="127"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="115">
+      <c r="B5" s="87">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116">
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117">
+      <c r="E5" s="88"/>
+      <c r="F5" s="89">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="117"/>
-      <c r="H5" s="118">
+      <c r="G5" s="89"/>
+      <c r="H5" s="90">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119">
+      <c r="I5" s="90"/>
+      <c r="J5" s="77">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="120"/>
-      <c r="L5" s="121"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="79"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="114">
+      <c r="B6" s="86">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114">
+      <c r="E6" s="86"/>
+      <c r="F6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114">
+      <c r="G6" s="86"/>
+      <c r="H6" s="86">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="77">
+      <c r="I6" s="86"/>
+      <c r="J6" s="102">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="78"/>
-      <c r="L6" s="79"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="104"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="105" t="s">
+      <c r="E7" s="92"/>
+      <c r="F7" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="104"/>
-      <c r="J7" s="80" t="s">
+      <c r="I7" s="92"/>
+      <c r="J7" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="107"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="106"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="85"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="110"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="91"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="115"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="103"/>
-      <c r="C11" s="110" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111" t="s">
+      <c r="D11" s="98"/>
+      <c r="E11" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="111"/>
-      <c r="G11" s="112" t="s">
+      <c r="F11" s="99"/>
+      <c r="G11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="112"/>
-      <c r="I11" s="113" t="s">
+      <c r="H11" s="100"/>
+      <c r="I11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="113"/>
+      <c r="J11" s="101"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="87" t="s">
+      <c r="L11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="87"/>
-      <c r="N11" s="89" t="s">
+      <c r="M11" s="91"/>
+      <c r="N11" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="89"/>
+      <c r="O11" s="113"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="103"/>
+      <c r="B12" s="127"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10357,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="91" t="s">
+      <c r="F33" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="91"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="115"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="115"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="87" t="s">
+      <c r="G34" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="H34" s="112"/>
+      <c r="I34" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="101" t="s">
+      <c r="J34" s="114"/>
+      <c r="K34" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
+      <c r="L34" s="126"/>
+      <c r="M34" s="126"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="93" t="s">
+      <c r="K35" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="94"/>
+      <c r="L35" s="118"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10466,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="95">
+      <c r="K36" s="119">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="96"/>
+      <c r="L36" s="120"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10507,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="97">
+      <c r="K37" s="121">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="98"/>
+      <c r="L37" s="122"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10548,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="99">
+      <c r="K38" s="123">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="100"/>
+      <c r="L38" s="124"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10696,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="86" t="s">
+      <c r="B50" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10778,34 +10778,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10822,6 +10794,34 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17902,7 +17902,7 @@
         <v>201</v>
       </c>
       <c r="B2" s="76">
-        <v>4</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854BE393-4CB5-4A9C-B6EC-CFE1714BE6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBA659A-DE0C-4E1B-8DBB-035F61351815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1460,73 +1460,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1556,6 +1489,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1605,6 +1541,70 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1639,7 +1639,16 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1651,16 +1660,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8413,6 +8413,317 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="4">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8560,317 +8871,6 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="8">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="122" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82" t="s">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="124"/>
+      <c r="F4" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82" t="s">
+      <c r="G4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="87">
+      <c r="B5" s="115">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88">
+      <c r="C5" s="115"/>
+      <c r="D5" s="116">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="89">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="89"/>
-      <c r="H5" s="90">
+      <c r="G5" s="117"/>
+      <c r="H5" s="118">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="77">
+      <c r="I5" s="118"/>
+      <c r="J5" s="119">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="79"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="86">
+      <c r="B6" s="114">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86">
+      <c r="C6" s="114"/>
+      <c r="D6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86">
+      <c r="E6" s="114"/>
+      <c r="F6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86">
+      <c r="G6" s="114"/>
+      <c r="H6" s="114">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="102">
+      <c r="I6" s="114"/>
+      <c r="J6" s="77">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="103"/>
-      <c r="L6" s="104"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="105" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="80" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="110"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="115"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="127"/>
-      <c r="C11" s="98" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="99" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="100" t="s">
+      <c r="F11" s="111"/>
+      <c r="G11" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="101" t="s">
+      <c r="H11" s="112"/>
+      <c r="I11" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="101"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="91" t="s">
+      <c r="L11" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="91"/>
-      <c r="N11" s="113" t="s">
+      <c r="M11" s="87"/>
+      <c r="N11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="113"/>
+      <c r="O11" s="89"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="127"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10357,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="115" t="s">
+      <c r="F33" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="91" t="s">
+      <c r="G34" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="112"/>
-      <c r="I34" s="113" t="s">
+      <c r="H34" s="88"/>
+      <c r="I34" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="114"/>
-      <c r="K34" s="125" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="117" t="s">
+      <c r="K35" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="118"/>
+      <c r="L35" s="94"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10466,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="119">
+      <c r="K36" s="95">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="120"/>
+      <c r="L36" s="96"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10507,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K37" s="97">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="122"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10548,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="123">
+      <c r="K38" s="99">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="124"/>
+      <c r="L38" s="100"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10696,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="111" t="s">
+      <c r="B50" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10778,6 +10778,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10794,34 +10822,6 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17894,7 +17894,7 @@
         <v>200</v>
       </c>
       <c r="B1" s="75">
-        <v>46190</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -17902,7 +17902,7 @@
         <v>201</v>
       </c>
       <c r="B2" s="76">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBA659A-DE0C-4E1B-8DBB-035F61351815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED1EFE5-FFB9-4418-A7C3-0B7729C0018A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1460,6 +1460,73 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1489,9 +1556,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1541,70 +1605,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1627,7 +1627,16 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1639,16 +1648,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -8413,154 +8413,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
@@ -8694,16 +8546,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8723,7 +8575,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8871,6 +8723,154 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124" t="s">
+      <c r="C4" s="82"/>
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="124"/>
-      <c r="J4" s="125" t="s">
+      <c r="I4" s="82"/>
+      <c r="J4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="126"/>
-      <c r="L4" s="127"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="115">
+      <c r="B5" s="87">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116">
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117">
+      <c r="E5" s="88"/>
+      <c r="F5" s="89">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="117"/>
-      <c r="H5" s="118">
+      <c r="G5" s="89"/>
+      <c r="H5" s="90">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119">
+      <c r="I5" s="90"/>
+      <c r="J5" s="77">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="120"/>
-      <c r="L5" s="121"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="79"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="114">
+      <c r="B6" s="86">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114">
+      <c r="C6" s="86"/>
+      <c r="D6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114">
+      <c r="E6" s="86"/>
+      <c r="F6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114">
+      <c r="G6" s="86"/>
+      <c r="H6" s="86">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="77">
+      <c r="I6" s="86"/>
+      <c r="J6" s="102">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="78"/>
-      <c r="L6" s="79"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="104"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="105" t="s">
+      <c r="E7" s="92"/>
+      <c r="F7" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="104"/>
-      <c r="J7" s="80" t="s">
+      <c r="I7" s="92"/>
+      <c r="J7" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="107"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="106"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="85"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="110"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="91"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="115"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="103"/>
-      <c r="C11" s="110" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111" t="s">
+      <c r="D11" s="98"/>
+      <c r="E11" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="111"/>
-      <c r="G11" s="112" t="s">
+      <c r="F11" s="99"/>
+      <c r="G11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="112"/>
-      <c r="I11" s="113" t="s">
+      <c r="H11" s="100"/>
+      <c r="I11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="113"/>
+      <c r="J11" s="101"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="87" t="s">
+      <c r="L11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="87"/>
-      <c r="N11" s="89" t="s">
+      <c r="M11" s="91"/>
+      <c r="N11" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="89"/>
+      <c r="O11" s="113"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="103"/>
+      <c r="B12" s="127"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10357,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="91" t="s">
+      <c r="F33" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="91"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="115"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="115"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="87" t="s">
+      <c r="G34" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="H34" s="112"/>
+      <c r="I34" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="101" t="s">
+      <c r="J34" s="114"/>
+      <c r="K34" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
+      <c r="L34" s="126"/>
+      <c r="M34" s="126"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="93" t="s">
+      <c r="K35" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="94"/>
+      <c r="L35" s="118"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10466,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="95">
+      <c r="K36" s="119">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="96"/>
+      <c r="L36" s="120"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10507,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="97">
+      <c r="K37" s="121">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="98"/>
+      <c r="L37" s="122"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10548,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="99">
+      <c r="K38" s="123">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="100"/>
+      <c r="L38" s="124"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10696,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="86" t="s">
+      <c r="B50" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10778,34 +10778,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10822,6 +10794,34 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17894,7 +17894,7 @@
         <v>200</v>
       </c>
       <c r="B1" s="75">
-        <v>46191</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -17902,7 +17902,7 @@
         <v>201</v>
       </c>
       <c r="B2" s="76">
-        <v>6.1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED1EFE5-FFB9-4418-A7C3-0B7729C0018A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE9C641-B725-43AC-B827-03EA61732C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="203">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t>Version</t>
+  </si>
+  <si>
+    <t>Test Update</t>
   </si>
 </sst>
 </file>
@@ -1460,73 +1463,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1556,6 +1492,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1605,6 +1544,70 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1625,18 +1628,6 @@
           <bgColor theme="4" tint="0.79979857783745845"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1661,6 +1652,18 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2106,7 +2109,7 @@
                   <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2534,7 +2537,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>74</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>63</c:v>
@@ -3827,7 +3830,7 @@
                   <c:v>3036</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7696</c:v>
+                  <c:v>9196</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8221</c:v>
@@ -8413,169 +8416,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8725,16 +8565,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8754,7 +8594,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8871,6 +8711,169 @@
   <dataFields count="2">
     <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9110,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="122" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82" t="s">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="124"/>
+      <c r="F4" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82" t="s">
+      <c r="G4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="87">
+      <c r="B5" s="115">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>137</v>
-      </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88">
+        <v>138</v>
+      </c>
+      <c r="C5" s="115"/>
+      <c r="D5" s="116">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="89">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>71</v>
-      </c>
-      <c r="G5" s="89"/>
-      <c r="H5" s="90">
+        <v>72</v>
+      </c>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>74</v>
-      </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="77">
+        <v>75</v>
+      </c>
+      <c r="I5" s="118"/>
+      <c r="J5" s="119">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="79"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="86">
+      <c r="B6" s="114">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>179966</v>
-      </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86">
+        <v>181466</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86">
+      <c r="E6" s="114"/>
+      <c r="F6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>103926</v>
-      </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86">
+        <v>105426</v>
+      </c>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>113190</v>
-      </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="102">
+        <v>114690</v>
+      </c>
+      <c r="I6" s="114"/>
+      <c r="J6" s="77">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="103"/>
-      <c r="L6" s="104"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="105" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="80" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="110"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="115"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="127"/>
-      <c r="C11" s="98" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="99" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="100" t="s">
+      <c r="F11" s="111"/>
+      <c r="G11" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="101" t="s">
+      <c r="H11" s="112"/>
+      <c r="I11" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="101"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="91" t="s">
+      <c r="L11" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="91"/>
-      <c r="N11" s="113" t="s">
+      <c r="M11" s="87"/>
+      <c r="N11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="113"/>
+      <c r="O11" s="89"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="127"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -9829,36 +9832,36 @@
       </c>
       <c r="E22" s="23">
         <f>COUNTIFS(Inventory!D2:D1000,B22,Inventory!H2:H1000,"NO")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="24">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B22,Inventory!H2:H1000,"NO")</f>
-        <v>2472</v>
+        <v>3972</v>
       </c>
       <c r="G22" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="26">
         <f t="shared" si="1"/>
-        <v>7696</v>
+        <v>9196</v>
       </c>
       <c r="I22" s="27">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="J22" s="27">
         <f t="shared" si="3"/>
-        <v>0.6787941787941788</v>
+        <v>0.56807307525010875</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="28">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B22,Inventory!I2:I1000,"Not Retired")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M22" s="29">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B22,Inventory!I2:I1000,"Not Retired")</f>
-        <v>7696</v>
+        <v>9196</v>
       </c>
       <c r="N22" s="30">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B22,Inventory!I2:I1000,"Retired")</f>
@@ -10315,36 +10318,36 @@
       </c>
       <c r="E31" s="1">
         <f t="shared" si="4"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="4"/>
-        <v>103926</v>
+        <v>105426</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="4"/>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H31" s="33">
         <f t="shared" si="4"/>
-        <v>179966</v>
+        <v>181466</v>
       </c>
       <c r="I31" s="34">
         <f t="shared" si="2"/>
-        <v>0.48175182481751827</v>
+        <v>0.47826086956521741</v>
       </c>
       <c r="J31" s="34">
         <f t="shared" si="3"/>
-        <v>0.42252425458142095</v>
+        <v>0.41903166433381461</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="1">
         <f ca="1">SUM(L13:L30)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M31" s="33">
         <f ca="1">SUM(M13:M30)</f>
-        <v>113190</v>
+        <v>114690</v>
       </c>
       <c r="N31" s="1">
         <f ca="1">SUM(N13:N30)</f>
@@ -10357,22 +10360,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="115" t="s">
+      <c r="F33" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10390,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="91" t="s">
+      <c r="G34" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="112"/>
-      <c r="I34" s="113" t="s">
+      <c r="H34" s="88"/>
+      <c r="I34" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="114"/>
-      <c r="K34" s="125" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10430,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="117" t="s">
+      <c r="K35" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="118"/>
+      <c r="L35" s="94"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10452,11 +10455,11 @@
       </c>
       <c r="G36" s="28">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H36" s="43">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>77802</v>
+        <v>79302</v>
       </c>
       <c r="I36" s="30">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
@@ -10466,14 +10469,14 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="119">
+      <c r="K36" s="95">
         <f ca="1">G36+I36</f>
-        <v>71</v>
-      </c>
-      <c r="L36" s="120"/>
+        <v>72</v>
+      </c>
+      <c r="L36" s="96"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
-        <v>103926</v>
+        <v>105426</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10507,11 +10510,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K37" s="97">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="122"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10534,11 +10537,11 @@
       </c>
       <c r="G38" s="1">
         <f t="shared" ref="G38:J38" ca="1" si="5">G36+G37</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H38" s="33">
         <f t="shared" ca="1" si="5"/>
-        <v>113190</v>
+        <v>114690</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -10548,14 +10551,14 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="123">
+      <c r="K38" s="99">
         <f ca="1">K36+K37</f>
-        <v>137</v>
-      </c>
-      <c r="L38" s="124"/>
+        <v>138</v>
+      </c>
+      <c r="L38" s="100"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
-        <v>179966</v>
+        <v>181466</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10674,11 +10677,11 @@
       </c>
       <c r="C47" s="28">
         <f>COUNTIF(Inventory!G2:G1000,"-")</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D47" s="43">
         <f>SUMIF(Inventory!G2:G1000,"-",Inventory!E2:E1000)</f>
-        <v>68767</v>
+        <v>70267</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10687,20 +10690,20 @@
       </c>
       <c r="C48" s="35">
         <f>SUM(C35:C47)</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D48" s="45">
         <f>SUM(D35:D47)</f>
-        <v>179479</v>
+        <v>180979</v>
       </c>
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="111" t="s">
+      <c r="B50" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10757,7 +10760,7 @@
       </c>
       <c r="E55" s="28">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10766,7 +10769,7 @@
       </c>
       <c r="C56" s="11">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>14</v>
@@ -10778,6 +10781,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10794,34 +10825,6 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15130,16 +15133,30 @@
         <f t="shared" si="5"/>
         <v>138</v>
       </c>
-      <c r="B139" s="66"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="68"/>
-      <c r="E139" s="66"/>
-      <c r="F139" s="66"/>
-      <c r="G139" s="66"/>
-      <c r="H139" s="68"/>
+      <c r="B139" s="66">
+        <v>43099</v>
+      </c>
+      <c r="C139" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="D139" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="E139" s="66">
+        <v>1500</v>
+      </c>
+      <c r="F139" s="66">
+        <v>2026</v>
+      </c>
+      <c r="G139" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="H139" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I139" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -17894,7 +17911,7 @@
         <v>200</v>
       </c>
       <c r="B1" s="75">
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE9C641-B725-43AC-B827-03EA61732C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC77AA-4B95-448F-ACCE-017DC0C13B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="202">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -673,9 +673,6 @@
   </si>
   <si>
     <t>Version</t>
-  </si>
-  <si>
-    <t>Test Update</t>
   </si>
 </sst>
 </file>
@@ -1463,6 +1460,73 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1492,9 +1556,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1544,70 +1605,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1642,7 +1639,16 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1654,16 +1660,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2109,7 +2106,7 @@
                   <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>72</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2537,7 +2534,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>75</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>63</c:v>
@@ -3830,7 +3827,7 @@
                   <c:v>3036</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9196</c:v>
+                  <c:v>7696</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8221</c:v>
@@ -8416,6 +8413,317 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="4">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8563,317 +8871,6 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="8">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9110,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124" t="s">
+      <c r="C4" s="82"/>
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="124"/>
-      <c r="J4" s="125" t="s">
+      <c r="I4" s="82"/>
+      <c r="J4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="126"/>
-      <c r="L4" s="127"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="115">
+      <c r="B5" s="87">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>138</v>
-      </c>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116">
+        <v>137</v>
+      </c>
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117">
+      <c r="E5" s="88"/>
+      <c r="F5" s="89">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>72</v>
-      </c>
-      <c r="G5" s="117"/>
-      <c r="H5" s="118">
+        <v>71</v>
+      </c>
+      <c r="G5" s="89"/>
+      <c r="H5" s="90">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>75</v>
-      </c>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119">
+        <v>74</v>
+      </c>
+      <c r="I5" s="90"/>
+      <c r="J5" s="77">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="120"/>
-      <c r="L5" s="121"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="79"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="114">
+      <c r="B6" s="86">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>181466</v>
-      </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114">
+        <v>179966</v>
+      </c>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114">
+      <c r="E6" s="86"/>
+      <c r="F6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>105426</v>
-      </c>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114">
+        <v>103926</v>
+      </c>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>114690</v>
-      </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="77">
+        <v>113190</v>
+      </c>
+      <c r="I6" s="86"/>
+      <c r="J6" s="102">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="78"/>
-      <c r="L6" s="79"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="104"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="105" t="s">
+      <c r="E7" s="92"/>
+      <c r="F7" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="104"/>
-      <c r="J7" s="80" t="s">
+      <c r="I7" s="92"/>
+      <c r="J7" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="107"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="106"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="85"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="110"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="91"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="115"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="103"/>
-      <c r="C11" s="110" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111" t="s">
+      <c r="D11" s="98"/>
+      <c r="E11" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="111"/>
-      <c r="G11" s="112" t="s">
+      <c r="F11" s="99"/>
+      <c r="G11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="112"/>
-      <c r="I11" s="113" t="s">
+      <c r="H11" s="100"/>
+      <c r="I11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="113"/>
+      <c r="J11" s="101"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="87" t="s">
+      <c r="L11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="87"/>
-      <c r="N11" s="89" t="s">
+      <c r="M11" s="91"/>
+      <c r="N11" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="89"/>
+      <c r="O11" s="113"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="103"/>
+      <c r="B12" s="127"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -9832,36 +9829,36 @@
       </c>
       <c r="E22" s="23">
         <f>COUNTIFS(Inventory!D2:D1000,B22,Inventory!H2:H1000,"NO")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" s="24">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B22,Inventory!H2:H1000,"NO")</f>
-        <v>3972</v>
+        <v>2472</v>
       </c>
       <c r="G22" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="26">
         <f t="shared" si="1"/>
-        <v>9196</v>
+        <v>7696</v>
       </c>
       <c r="I22" s="27">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5</v>
       </c>
       <c r="J22" s="27">
         <f t="shared" si="3"/>
-        <v>0.56807307525010875</v>
+        <v>0.6787941787941788</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="28">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B22,Inventory!I2:I1000,"Not Retired")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M22" s="29">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B22,Inventory!I2:I1000,"Not Retired")</f>
-        <v>9196</v>
+        <v>7696</v>
       </c>
       <c r="N22" s="30">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B22,Inventory!I2:I1000,"Retired")</f>
@@ -10318,36 +10315,36 @@
       </c>
       <c r="E31" s="1">
         <f t="shared" si="4"/>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="4"/>
-        <v>105426</v>
+        <v>103926</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="4"/>
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H31" s="33">
         <f t="shared" si="4"/>
-        <v>181466</v>
+        <v>179966</v>
       </c>
       <c r="I31" s="34">
         <f t="shared" si="2"/>
-        <v>0.47826086956521741</v>
+        <v>0.48175182481751827</v>
       </c>
       <c r="J31" s="34">
         <f t="shared" si="3"/>
-        <v>0.41903166433381461</v>
+        <v>0.42252425458142095</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="1">
         <f ca="1">SUM(L13:L30)</f>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M31" s="33">
         <f ca="1">SUM(M13:M30)</f>
-        <v>114690</v>
+        <v>113190</v>
       </c>
       <c r="N31" s="1">
         <f ca="1">SUM(N13:N30)</f>
@@ -10360,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="91" t="s">
+      <c r="F33" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="91"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="115"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="115"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10390,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="87" t="s">
+      <c r="G34" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="H34" s="112"/>
+      <c r="I34" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="101" t="s">
+      <c r="J34" s="114"/>
+      <c r="K34" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
+      <c r="L34" s="126"/>
+      <c r="M34" s="126"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10430,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="93" t="s">
+      <c r="K35" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="94"/>
+      <c r="L35" s="118"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10455,11 +10452,11 @@
       </c>
       <c r="G36" s="28">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H36" s="43">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>79302</v>
+        <v>77802</v>
       </c>
       <c r="I36" s="30">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
@@ -10469,14 +10466,14 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="95">
+      <c r="K36" s="119">
         <f ca="1">G36+I36</f>
-        <v>72</v>
-      </c>
-      <c r="L36" s="96"/>
+        <v>71</v>
+      </c>
+      <c r="L36" s="120"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
-        <v>105426</v>
+        <v>103926</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10510,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="97">
+      <c r="K37" s="121">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="98"/>
+      <c r="L37" s="122"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10537,11 +10534,11 @@
       </c>
       <c r="G38" s="1">
         <f t="shared" ref="G38:J38" ca="1" si="5">G36+G37</f>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H38" s="33">
         <f t="shared" ca="1" si="5"/>
-        <v>114690</v>
+        <v>113190</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -10551,14 +10548,14 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="99">
+      <c r="K38" s="123">
         <f ca="1">K36+K37</f>
-        <v>138</v>
-      </c>
-      <c r="L38" s="100"/>
+        <v>137</v>
+      </c>
+      <c r="L38" s="124"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
-        <v>181466</v>
+        <v>179966</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10677,11 +10674,11 @@
       </c>
       <c r="C47" s="28">
         <f>COUNTIF(Inventory!G2:G1000,"-")</f>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D47" s="43">
         <f>SUMIF(Inventory!G2:G1000,"-",Inventory!E2:E1000)</f>
-        <v>70267</v>
+        <v>68767</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10690,20 +10687,20 @@
       </c>
       <c r="C48" s="35">
         <f>SUM(C35:C47)</f>
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D48" s="45">
         <f>SUM(D35:D47)</f>
-        <v>180979</v>
+        <v>179479</v>
       </c>
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="86" t="s">
+      <c r="B50" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10760,7 +10757,7 @@
       </c>
       <c r="E55" s="28">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10769,7 +10766,7 @@
       </c>
       <c r="C56" s="11">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>14</v>
@@ -10781,34 +10778,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10825,6 +10794,34 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15133,30 +15130,16 @@
         <f t="shared" si="5"/>
         <v>138</v>
       </c>
-      <c r="B139" s="66">
-        <v>43099</v>
-      </c>
-      <c r="C139" s="67" t="s">
-        <v>202</v>
-      </c>
-      <c r="D139" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="E139" s="66">
-        <v>1500</v>
-      </c>
-      <c r="F139" s="66">
-        <v>2026</v>
-      </c>
-      <c r="G139" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="H139" s="68" t="s">
-        <v>55</v>
-      </c>
+      <c r="B139" s="66"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="68"/>
+      <c r="E139" s="66"/>
+      <c r="F139" s="66"/>
+      <c r="G139" s="66"/>
+      <c r="H139" s="68"/>
       <c r="I139" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>Not Retired</v>
+        <v/>
       </c>
     </row>
     <row r="140" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC77AA-4B95-448F-ACCE-017DC0C13B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FF6453-4F9D-4031-9654-E7A35E56647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1460,73 +1460,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1556,6 +1489,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1605,6 +1541,70 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1627,7 +1627,16 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1639,16 +1648,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -8413,154 +8413,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
@@ -8694,16 +8546,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8723,7 +8575,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8871,6 +8723,154 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9107,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="122" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82" t="s">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="124"/>
+      <c r="F4" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82" t="s">
+      <c r="G4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="87">
+      <c r="B5" s="115">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>137</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88">
+      <c r="C5" s="115"/>
+      <c r="D5" s="116">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="89">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>71</v>
       </c>
-      <c r="G5" s="89"/>
-      <c r="H5" s="90">
+      <c r="G5" s="117"/>
+      <c r="H5" s="118">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>74</v>
       </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="77">
+      <c r="I5" s="118"/>
+      <c r="J5" s="119">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="79"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="86">
+      <c r="B6" s="114">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>179966</v>
       </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86">
+      <c r="C6" s="114"/>
+      <c r="D6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86">
+      <c r="E6" s="114"/>
+      <c r="F6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>103926</v>
       </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86">
+      <c r="G6" s="114"/>
+      <c r="H6" s="114">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>113190</v>
       </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="102">
+      <c r="I6" s="114"/>
+      <c r="J6" s="77">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="103"/>
-      <c r="L6" s="104"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="105" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="80" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="110"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="115"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="127"/>
-      <c r="C11" s="98" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="99" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="100" t="s">
+      <c r="F11" s="111"/>
+      <c r="G11" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="101" t="s">
+      <c r="H11" s="112"/>
+      <c r="I11" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="101"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="91" t="s">
+      <c r="L11" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="91"/>
-      <c r="N11" s="113" t="s">
+      <c r="M11" s="87"/>
+      <c r="N11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="113"/>
+      <c r="O11" s="89"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="127"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -10357,22 +10357,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="115" t="s">
+      <c r="F33" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10387,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="91" t="s">
+      <c r="G34" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="112"/>
-      <c r="I34" s="113" t="s">
+      <c r="H34" s="88"/>
+      <c r="I34" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="114"/>
-      <c r="K34" s="125" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10427,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="117" t="s">
+      <c r="K35" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="118"/>
+      <c r="L35" s="94"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10466,11 +10466,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="119">
+      <c r="K36" s="95">
         <f ca="1">G36+I36</f>
         <v>71</v>
       </c>
-      <c r="L36" s="120"/>
+      <c r="L36" s="96"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
         <v>103926</v>
@@ -10507,11 +10507,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K37" s="97">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="122"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10548,11 +10548,11 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="123">
+      <c r="K38" s="99">
         <f ca="1">K36+K37</f>
         <v>137</v>
       </c>
-      <c r="L38" s="124"/>
+      <c r="L38" s="100"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
         <v>179966</v>
@@ -10696,11 +10696,11 @@
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="111" t="s">
+      <c r="B50" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10778,6 +10778,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10794,34 +10822,6 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17894,7 +17894,7 @@
         <v>200</v>
       </c>
       <c r="B1" s="75">
-        <v>46190</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FF6453-4F9D-4031-9654-E7A35E56647D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB1B7F-593B-4238-AEE7-D752E69E8EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="203">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -673,6 +673,9 @@
   </si>
   <si>
     <t>Version</t>
+  </si>
+  <si>
+    <t>The Darksaber</t>
   </si>
 </sst>
 </file>
@@ -1460,6 +1463,73 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1489,9 +1559,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1541,70 +1608,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1625,18 +1628,6 @@
           <bgColor theme="4" tint="0.79979857783745845"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1661,6 +1652,18 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2106,7 +2109,7 @@
                   <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2534,7 +2537,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>74</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>63</c:v>
@@ -3800,7 +3803,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>45783</c:v>
+                  <c:v>46061</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>22286</c:v>
@@ -8413,169 +8416,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8725,16 +8565,16 @@
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8754,7 +8594,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8871,6 +8711,169 @@
   <dataFields count="2">
     <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9107,190 +9110,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124" t="s">
+      <c r="C4" s="82"/>
+      <c r="D4" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="124"/>
-      <c r="H4" s="124" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="124"/>
-      <c r="J4" s="125" t="s">
+      <c r="I4" s="82"/>
+      <c r="J4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="126"/>
-      <c r="L4" s="127"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="115">
+      <c r="B5" s="87">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>137</v>
-      </c>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116">
+        <v>138</v>
+      </c>
+      <c r="C5" s="87"/>
+      <c r="D5" s="88">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="117">
+      <c r="E5" s="88"/>
+      <c r="F5" s="89">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>71</v>
-      </c>
-      <c r="G5" s="117"/>
-      <c r="H5" s="118">
+        <v>72</v>
+      </c>
+      <c r="G5" s="89"/>
+      <c r="H5" s="90">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>74</v>
-      </c>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119">
+        <v>75</v>
+      </c>
+      <c r="I5" s="90"/>
+      <c r="J5" s="77">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>63</v>
       </c>
-      <c r="K5" s="120"/>
-      <c r="L5" s="121"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="79"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="114">
+      <c r="B6" s="86">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>179966</v>
-      </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114">
+        <v>180244</v>
+      </c>
+      <c r="C6" s="86"/>
+      <c r="D6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114">
+      <c r="E6" s="86"/>
+      <c r="F6" s="86">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>103926</v>
-      </c>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114">
+        <v>104204</v>
+      </c>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>113190</v>
-      </c>
-      <c r="I6" s="114"/>
-      <c r="J6" s="77">
+        <v>113468</v>
+      </c>
+      <c r="I6" s="86"/>
+      <c r="J6" s="102">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>66776</v>
       </c>
-      <c r="K6" s="78"/>
-      <c r="L6" s="79"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="104"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="105" t="s">
+      <c r="E7" s="92"/>
+      <c r="F7" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="104"/>
-      <c r="J7" s="80" t="s">
+      <c r="I7" s="92"/>
+      <c r="J7" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="82"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="107"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="106"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="85"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="110"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="91"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+      <c r="K10" s="115"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="115"/>
+      <c r="O10" s="115"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="103"/>
-      <c r="C11" s="110" t="s">
+      <c r="B11" s="127"/>
+      <c r="C11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111" t="s">
+      <c r="D11" s="98"/>
+      <c r="E11" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="111"/>
-      <c r="G11" s="112" t="s">
+      <c r="F11" s="99"/>
+      <c r="G11" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="112"/>
-      <c r="I11" s="113" t="s">
+      <c r="H11" s="100"/>
+      <c r="I11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="113"/>
+      <c r="J11" s="101"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="87" t="s">
+      <c r="L11" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="87"/>
-      <c r="N11" s="89" t="s">
+      <c r="M11" s="91"/>
+      <c r="N11" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="89"/>
+      <c r="O11" s="113"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="103"/>
+      <c r="B12" s="127"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -9343,36 +9346,36 @@
       </c>
       <c r="E13" s="11">
         <f>COUNTIFS(Inventory!D2:D1000,B13,Inventory!H2:H1000,"NO")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" s="12">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B13,Inventory!H2:H1000,"NO")</f>
-        <v>32809</v>
+        <v>33087</v>
       </c>
       <c r="G13" s="13">
         <f t="shared" ref="G13:G30" si="0">C13+E13</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" ref="H13:H30" si="1">D13+F13</f>
-        <v>45783</v>
+        <v>46061</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" ref="I13:I31" si="2">IF(G13=0,"",C13/G13)</f>
-        <v>0.375</v>
+        <v>0.36734693877551022</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ref="J13:J31" si="3">IF(H13=0,"",D13/H13)</f>
-        <v>0.2833802939955879</v>
+        <v>0.28166995940166301</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="16">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B13,Inventory!I2:I1000,"Not Retired")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M13" s="17">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B13,Inventory!I2:I1000,"Not Retired")</f>
-        <v>24838</v>
+        <v>25116</v>
       </c>
       <c r="N13" s="18">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B13,Inventory!I2:I1000,"Retired")</f>
@@ -10315,36 +10318,36 @@
       </c>
       <c r="E31" s="1">
         <f t="shared" si="4"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="4"/>
-        <v>103926</v>
+        <v>104204</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="4"/>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H31" s="33">
         <f t="shared" si="4"/>
-        <v>179966</v>
+        <v>180244</v>
       </c>
       <c r="I31" s="34">
         <f t="shared" si="2"/>
-        <v>0.48175182481751827</v>
+        <v>0.47826086956521741</v>
       </c>
       <c r="J31" s="34">
         <f t="shared" si="3"/>
-        <v>0.42252425458142095</v>
+        <v>0.42187257273473738</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="1">
         <f ca="1">SUM(L13:L30)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M31" s="33">
         <f ca="1">SUM(M13:M30)</f>
-        <v>113190</v>
+        <v>113468</v>
       </c>
       <c r="N31" s="1">
         <f ca="1">SUM(N13:N30)</f>
@@ -10357,22 +10360,22 @@
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="92"/>
-      <c r="D33" s="92"/>
+      <c r="C33" s="116"/>
+      <c r="D33" s="116"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="91" t="s">
+      <c r="F33" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="91"/>
+      <c r="G33" s="115"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="115"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="115"/>
+      <c r="M33" s="115"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10387,19 +10390,19 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="87" t="s">
+      <c r="G34" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="H34" s="112"/>
+      <c r="I34" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="90"/>
-      <c r="K34" s="101" t="s">
+      <c r="J34" s="114"/>
+      <c r="K34" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="102"/>
-      <c r="M34" s="102"/>
+      <c r="L34" s="126"/>
+      <c r="M34" s="126"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10427,10 +10430,10 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="93" t="s">
+      <c r="K35" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="94"/>
+      <c r="L35" s="118"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
@@ -10452,11 +10455,11 @@
       </c>
       <c r="G36" s="28">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H36" s="43">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>77802</v>
+        <v>78080</v>
       </c>
       <c r="I36" s="30">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
@@ -10466,14 +10469,14 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
         <v>26124</v>
       </c>
-      <c r="K36" s="95">
+      <c r="K36" s="119">
         <f ca="1">G36+I36</f>
-        <v>71</v>
-      </c>
-      <c r="L36" s="96"/>
+        <v>72</v>
+      </c>
+      <c r="L36" s="120"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
-        <v>103926</v>
+        <v>104204</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10507,11 +10510,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="97">
+      <c r="K37" s="121">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="98"/>
+      <c r="L37" s="122"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10534,11 +10537,11 @@
       </c>
       <c r="G38" s="1">
         <f t="shared" ref="G38:J38" ca="1" si="5">G36+G37</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H38" s="33">
         <f t="shared" ca="1" si="5"/>
-        <v>113190</v>
+        <v>113468</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" ca="1" si="5"/>
@@ -10548,14 +10551,14 @@
         <f t="shared" ca="1" si="5"/>
         <v>66776</v>
       </c>
-      <c r="K38" s="99">
+      <c r="K38" s="123">
         <f ca="1">K36+K37</f>
-        <v>137</v>
-      </c>
-      <c r="L38" s="100"/>
+        <v>138</v>
+      </c>
+      <c r="L38" s="124"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
-        <v>179966</v>
+        <v>180244</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10661,11 +10664,11 @@
       </c>
       <c r="C46" s="41">
         <f>COUNTIF(Inventory!G2:G1000,B46)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D46" s="42">
         <f>SUMIF(Inventory!G2:G1000,B46,Inventory!E2:E1000)</f>
-        <v>44423</v>
+        <v>44701</v>
       </c>
     </row>
     <row r="47" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10687,20 +10690,20 @@
       </c>
       <c r="C48" s="35">
         <f>SUM(C35:C47)</f>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D48" s="45">
         <f>SUM(D35:D47)</f>
-        <v>179479</v>
+        <v>179757</v>
       </c>
     </row>
     <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="86" t="s">
+      <c r="B50" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="86"/>
-      <c r="D50" s="86"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="111"/>
     </row>
     <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="36"/>
@@ -10757,7 +10760,7 @@
       </c>
       <c r="E55" s="28">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -10766,7 +10769,7 @@
       </c>
       <c r="C56" s="11">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>14</v>
@@ -10778,34 +10781,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="J8:L8"/>
@@ -10822,6 +10797,34 @@
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15130,16 +15133,30 @@
         <f t="shared" si="5"/>
         <v>138</v>
       </c>
-      <c r="B139" s="66"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="68"/>
-      <c r="E139" s="66"/>
-      <c r="F139" s="66"/>
-      <c r="G139" s="66"/>
-      <c r="H139" s="68"/>
+      <c r="B139" s="66">
+        <v>40917</v>
+      </c>
+      <c r="C139" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="D139" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E139" s="66">
+        <v>278</v>
+      </c>
+      <c r="F139" s="66">
+        <v>2026</v>
+      </c>
+      <c r="G139" s="66">
+        <v>2026</v>
+      </c>
+      <c r="H139" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I139" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEB1B7F-593B-4238-AEE7-D752E69E8EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C7102E-B6E8-49E6-9750-18DF6A0896E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="100" windowWidth="22630" windowHeight="20110" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19190" yWindow="230" windowWidth="19110" windowHeight="20110" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="210">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -676,6 +676,27 @@
   </si>
   <si>
     <t>The Darksaber</t>
+  </si>
+  <si>
+    <t>SEGA® Genesis™ Console</t>
+  </si>
+  <si>
+    <t>Peanuts: Snoopy's Doghouse</t>
+  </si>
+  <si>
+    <t>The Fast and The Furious Toyota Supra MK4</t>
+  </si>
+  <si>
+    <t>Dinosaur Fossils: Triceratops</t>
+  </si>
+  <si>
+    <t>Darth Vader (2002)</t>
+  </si>
+  <si>
+    <t>C-3PO (2001)</t>
+  </si>
+  <si>
+    <t>Stormtrooper (2001)</t>
   </si>
 </sst>
 </file>
@@ -1463,73 +1484,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1559,6 +1513,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1608,6 +1565,70 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1642,7 +1663,16 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1654,16 +1684,7 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2087,7 +2108,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$B$55:$B$56</c:f>
+              <c:f>Dashboard!$B$57:$B$58</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -2101,7 +2122,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard!$C$55:$C$56</c:f>
+              <c:f>Dashboard!$C$57:$C$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2109,7 +2130,7 @@
                   <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>72</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2518,7 +2539,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard!$D$55:$D$56</c:f>
+              <c:f>Dashboard!$D$57:$D$58</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -2537,10 +2558,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>75</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3803,7 +3824,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>46061</c:v>
+                  <c:v>47576</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>22286</c:v>
@@ -3812,10 +3833,10 @@
                   <c:v>41709</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11138</c:v>
+                  <c:v>12102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2824</c:v>
+                  <c:v>3116</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10854</c:v>
@@ -3833,7 +3854,7 @@
                   <c:v>7696</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8221</c:v>
+                  <c:v>8700</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2637</c:v>
@@ -3842,7 +3863,7 @@
                   <c:v>811</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3145</c:v>
+                  <c:v>4299</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>878</c:v>
@@ -8416,6 +8437,317 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="5"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="13"/>
+        <item t="default" sd="0"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="6"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="4">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
+  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="20">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item h="1" x="18"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="19">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="8" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="8">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
   <location ref="A2:C31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
@@ -8563,317 +8895,6 @@
   <dataFields count="2">
     <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Bricks" fld="4" baseField="3" baseItem="14" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="4">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="I2:K17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="16"/>
-        <item x="13"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="5"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item h="1" sd="0" x="13"/>
-        <item t="default" sd="0"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="6"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sets" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="6" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <formats count="4">
-    <format dxfId="8">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1">
-  <location ref="E5:G25" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="20">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item h="1" x="18"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="19">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="8" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Sets" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Bricks" fld="4" baseField="3" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="4">
     <format dxfId="12">
@@ -9087,7 +9108,7 @@
   <sheetPr>
     <tabColor rgb="FFDA3B30"/>
   </sheetPr>
-  <dimension ref="B1:R56"/>
+  <dimension ref="B1:R58"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -9110,190 +9131,190 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="122" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82" t="s">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82" t="s">
+      <c r="E4" s="124"/>
+      <c r="F4" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82" t="s">
+      <c r="G4" s="124"/>
+      <c r="H4" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="127"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="87">
+      <c r="B5" s="115">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>138</v>
-      </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88">
+        <v>146</v>
+      </c>
+      <c r="C5" s="115"/>
+      <c r="D5" s="116">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="89">
+      <c r="E5" s="116"/>
+      <c r="F5" s="117">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>72</v>
-      </c>
-      <c r="G5" s="89"/>
-      <c r="H5" s="90">
+        <v>80</v>
+      </c>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>75</v>
-      </c>
-      <c r="I5" s="90"/>
-      <c r="J5" s="77">
+        <v>79</v>
+      </c>
+      <c r="I5" s="118"/>
+      <c r="J5" s="119">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
-        <v>63</v>
-      </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="79"/>
+        <v>67</v>
+      </c>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="86">
+      <c r="B6" s="114">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>180244</v>
-      </c>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86">
+        <v>184648</v>
+      </c>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>76040</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86">
+      <c r="E6" s="114"/>
+      <c r="F6" s="114">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>104204</v>
-      </c>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86">
+        <v>108608</v>
+      </c>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>113468</v>
-      </c>
-      <c r="I6" s="86"/>
-      <c r="J6" s="102">
+        <v>116357</v>
+      </c>
+      <c r="I6" s="114"/>
+      <c r="J6" s="77">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
-        <v>66776</v>
-      </c>
-      <c r="K6" s="103"/>
-      <c r="L6" s="104"/>
+        <v>68291</v>
+      </c>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="61"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="92"/>
-      <c r="F7" s="93" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="105" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="80" t="s">
         <v>174</v>
       </c>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="108"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="110"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="85"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="115"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
     </row>
     <row r="11" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="127"/>
-      <c r="C11" s="98" t="s">
+      <c r="B11" s="103"/>
+      <c r="C11" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="99" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="111" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="100" t="s">
+      <c r="F11" s="111"/>
+      <c r="G11" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="100"/>
-      <c r="I11" s="101" t="s">
+      <c r="H11" s="112"/>
+      <c r="I11" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="101"/>
+      <c r="J11" s="113"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="91" t="s">
+      <c r="L11" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="91"/>
-      <c r="N11" s="113" t="s">
+      <c r="M11" s="87"/>
+      <c r="N11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="O11" s="113"/>
+      <c r="O11" s="89"/>
     </row>
     <row r="12" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="127"/>
+      <c r="B12" s="103"/>
       <c r="C12" s="3" t="s">
         <v>15</v>
       </c>
@@ -9346,27 +9367,27 @@
       </c>
       <c r="E13" s="11">
         <f>COUNTIFS(Inventory!D2:D1000,B13,Inventory!H2:H1000,"NO")</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F13" s="12">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B13,Inventory!H2:H1000,"NO")</f>
-        <v>33087</v>
+        <v>34602</v>
       </c>
       <c r="G13" s="13">
         <f t="shared" ref="G13:G30" si="0">C13+E13</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" ref="H13:H30" si="1">D13+F13</f>
-        <v>46061</v>
+        <v>47576</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" ref="I13:I31" si="2">IF(G13=0,"",C13/G13)</f>
-        <v>0.36734693877551022</v>
+        <v>0.33962264150943394</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ref="J13:J31" si="3">IF(H13=0,"",D13/H13)</f>
-        <v>0.28166995940166301</v>
+        <v>0.27270052127122918</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="16">
@@ -9379,11 +9400,11 @@
       </c>
       <c r="N13" s="18">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B13,Inventory!I2:I1000,"Retired")</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O13" s="19">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B13,Inventory!I2:I1000,"Retired")</f>
-        <v>20945</v>
+        <v>22460</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9508,36 +9529,36 @@
       </c>
       <c r="E16" s="23">
         <f>COUNTIFS(Inventory!D2:D1000,B16,Inventory!H2:H1000,"NO")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="24">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B16,Inventory!H2:H1000,"NO")</f>
-        <v>2880</v>
+        <v>3844</v>
       </c>
       <c r="G16" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="26">
         <f t="shared" si="1"/>
-        <v>11138</v>
+        <v>12102</v>
       </c>
       <c r="I16" s="27">
         <f t="shared" si="2"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J16" s="27">
         <f t="shared" si="3"/>
-        <v>0.74142574968576047</v>
+        <v>0.68236655098330856</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="28">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B16,Inventory!I2:I1000,"Not Retired")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" s="29">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B16,Inventory!I2:I1000,"Not Retired")</f>
-        <v>5203</v>
+        <v>6167</v>
       </c>
       <c r="N16" s="30">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B16,Inventory!I2:I1000,"Retired")</f>
@@ -9562,36 +9583,36 @@
       </c>
       <c r="E17" s="11">
         <f>COUNTIFS(Inventory!D2:D1000,B17,Inventory!H2:H1000,"NO")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="12">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B17,Inventory!H2:H1000,"NO")</f>
-        <v>1565</v>
+        <v>1857</v>
       </c>
       <c r="G17" s="13">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" si="1"/>
-        <v>2824</v>
+        <v>3116</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="2"/>
-        <v>0.44444444444444442</v>
+        <v>0.4</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="3"/>
-        <v>0.44582152974504247</v>
+        <v>0.40404364569961487</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="16">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B17,Inventory!I2:I1000,"Not Retired")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M17" s="17">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B17,Inventory!I2:I1000,"Not Retired")</f>
-        <v>2260</v>
+        <v>2552</v>
       </c>
       <c r="N17" s="18">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B17,Inventory!I2:I1000,"Retired")</f>
@@ -9886,36 +9907,36 @@
       </c>
       <c r="E23" s="11">
         <f>COUNTIFS(Inventory!D2:D1000,B23,Inventory!H2:H1000,"NO")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="12">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B23,Inventory!H2:H1000,"NO")</f>
-        <v>7976</v>
+        <v>8455</v>
       </c>
       <c r="G23" s="13">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
         <f t="shared" si="1"/>
-        <v>8221</v>
+        <v>8700</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="3"/>
-        <v>2.9801727283785429E-2</v>
+        <v>2.8160919540229885E-2</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="16">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B23,Inventory!I2:I1000,"Not Retired")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23" s="17">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B23,Inventory!I2:I1000,"Not Retired")</f>
-        <v>8221</v>
+        <v>8700</v>
       </c>
       <c r="N23" s="18">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B23,Inventory!I2:I1000,"Retired")</f>
@@ -10048,36 +10069,36 @@
       </c>
       <c r="E26" s="23">
         <f>COUNTIFS(Inventory!D2:D1000,B26,Inventory!H2:H1000,"NO")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="24">
         <f>SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B26,Inventory!H2:H1000,"NO")</f>
-        <v>0</v>
+        <v>1154</v>
       </c>
       <c r="G26" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="26">
         <f t="shared" si="1"/>
-        <v>3145</v>
+        <v>4299</v>
       </c>
       <c r="I26" s="27">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J26" s="27">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.73156548034426616</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="28">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B26,Inventory!I2:I1000,"Not Retired")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="29">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!D2:D1000,B26,Inventory!I2:I1000,"Not Retired")</f>
-        <v>3145</v>
+        <v>4299</v>
       </c>
       <c r="N26" s="30">
         <f ca="1">COUNTIFS(Inventory!D2:D1000,B26,Inventory!I2:I1000,"Retired")</f>
@@ -10318,64 +10339,64 @@
       </c>
       <c r="E31" s="1">
         <f t="shared" si="4"/>
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F31" s="33">
         <f t="shared" si="4"/>
-        <v>104204</v>
+        <v>108608</v>
       </c>
       <c r="G31" s="1">
         <f t="shared" si="4"/>
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="H31" s="33">
         <f t="shared" si="4"/>
-        <v>180244</v>
+        <v>184648</v>
       </c>
       <c r="I31" s="34">
         <f t="shared" si="2"/>
-        <v>0.47826086956521741</v>
+        <v>0.45205479452054792</v>
       </c>
       <c r="J31" s="34">
         <f t="shared" si="3"/>
-        <v>0.42187257273473738</v>
+        <v>0.41181058013084354</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="1">
         <f ca="1">SUM(L13:L30)</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M31" s="33">
         <f ca="1">SUM(M13:M30)</f>
-        <v>113468</v>
+        <v>116357</v>
       </c>
       <c r="N31" s="1">
         <f ca="1">SUM(N13:N30)</f>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O31" s="33">
         <f ca="1">SUM(O13:O30)</f>
-        <v>66776</v>
+        <v>68291</v>
       </c>
     </row>
     <row r="32" spans="2:15" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
       <c r="E33" s="55"/>
-      <c r="F33" s="115" t="s">
+      <c r="F33" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="91"/>
+      <c r="K33" s="91"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
       <c r="N33" s="55"/>
       <c r="O33" s="55"/>
     </row>
@@ -10390,32 +10411,32 @@
         <v>16</v>
       </c>
       <c r="F34" s="1"/>
-      <c r="G34" s="91" t="s">
+      <c r="G34" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="H34" s="112"/>
-      <c r="I34" s="113" t="s">
+      <c r="H34" s="88"/>
+      <c r="I34" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="114"/>
-      <c r="K34" s="125" t="s">
+      <c r="J34" s="90"/>
+      <c r="K34" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="126"/>
-      <c r="M34" s="126"/>
+      <c r="L34" s="102"/>
+      <c r="M34" s="102"/>
       <c r="R34" s="36"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="37">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="C35" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B35)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="38">
-        <f>SUMIF(Inventory!G2:G1000,B35,Inventory!E2:E1000)</f>
-        <v>560</v>
+        <f>SUMIF(Inventory!$G$2:$G$1000,B35,Inventory!$E$2:$E$1000)</f>
+        <v>702</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="6" t="s">
@@ -10430,66 +10451,66 @@
       <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K35" s="117" t="s">
+      <c r="K35" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="118"/>
+      <c r="L35" s="94"/>
       <c r="M35" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="39">
-        <v>2012</v>
-      </c>
-      <c r="C36" s="39">
+      <c r="B36" s="37">
+        <v>2003</v>
+      </c>
+      <c r="C36" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B36)</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="40">
-        <f>SUMIF(Inventory!G2:G1000,B36,Inventory!E2:E1000)</f>
-        <v>4287</v>
+        <v>2</v>
+      </c>
+      <c r="D36" s="38">
+        <f>SUMIF(Inventory!$G$2:$G$1000,B36,Inventory!$E$2:$E$1000)</f>
+        <v>813</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="28">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H36" s="43">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>78080</v>
+        <v>80969</v>
       </c>
       <c r="I36" s="30">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J36" s="46">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
-        <v>26124</v>
-      </c>
-      <c r="K36" s="119">
+        <v>27639</v>
+      </c>
+      <c r="K36" s="95">
         <f ca="1">G36+I36</f>
-        <v>72</v>
-      </c>
-      <c r="L36" s="120"/>
+        <v>80</v>
+      </c>
+      <c r="L36" s="96"/>
       <c r="M36" s="47">
         <f ca="1">H36+J36</f>
-        <v>104204</v>
+        <v>108608</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="37">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C37" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B37)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="38">
-        <f>SUMIF(Inventory!G2:G1000,B37,Inventory!E2:E1000)</f>
-        <v>708</v>
+        <f>SUMIF(Inventory!$G$2:$G$1000,B37,Inventory!$E$2:$E$1000)</f>
+        <v>560</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>9</v>
@@ -10510,11 +10531,11 @@
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
         <v>40652</v>
       </c>
-      <c r="K37" s="121">
+      <c r="K37" s="97">
         <f ca="1">G37+I37</f>
         <v>66</v>
       </c>
-      <c r="L37" s="122"/>
+      <c r="L37" s="98"/>
       <c r="M37" s="50">
         <f ca="1">H37+J37</f>
         <v>76040</v>
@@ -10522,56 +10543,56 @@
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="39">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C38" s="39">
         <f>COUNTIF(Inventory!G2:G1000,B38)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D38" s="40">
         <f>SUMIF(Inventory!G2:G1000,B38,Inventory!E2:E1000)</f>
-        <v>4706</v>
+        <v>4287</v>
       </c>
       <c r="F38" s="32" t="s">
         <v>11</v>
       </c>
       <c r="G38" s="1">
         <f t="shared" ref="G38:J38" ca="1" si="5">G36+G37</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H38" s="33">
         <f t="shared" ca="1" si="5"/>
-        <v>113468</v>
+        <v>116357</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J38" s="33">
         <f t="shared" ca="1" si="5"/>
-        <v>66776</v>
-      </c>
-      <c r="K38" s="123">
+        <v>68291</v>
+      </c>
+      <c r="K38" s="99">
         <f ca="1">K36+K37</f>
-        <v>138</v>
-      </c>
-      <c r="L38" s="124"/>
+        <v>146</v>
+      </c>
+      <c r="L38" s="100"/>
       <c r="M38" s="33">
         <f ca="1">M36+M37</f>
-        <v>180244</v>
+        <v>184648</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="37">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C39" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B39)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D39" s="38">
         <f>SUMIF(Inventory!G2:G1000,B39,Inventory!E2:E1000)</f>
-        <v>3175</v>
+        <v>708</v>
       </c>
       <c r="F39" s="36"/>
       <c r="G39" s="36"/>
@@ -10579,15 +10600,15 @@
     </row>
     <row r="40" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="39">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C40" s="39">
         <f>COUNTIF(Inventory!G2:G1000,B40)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D40" s="40">
         <f>SUMIF(Inventory!G2:G1000,B40,Inventory!E2:E1000)</f>
-        <v>5981</v>
+        <v>4706</v>
       </c>
       <c r="F40" s="36"/>
       <c r="G40" s="36"/>
@@ -10595,132 +10616,146 @@
     </row>
     <row r="41" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="37">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C41" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B41)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D41" s="38">
         <f>SUMIF(Inventory!G2:G1000,B41,Inventory!E2:E1000)</f>
-        <v>2574</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="42" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="39">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C42" s="39">
         <f>COUNTIF(Inventory!G2:G1000,B42)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D42" s="40">
         <f>SUMIF(Inventory!G2:G1000,B42,Inventory!E2:E1000)</f>
-        <v>8591</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="37">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C43" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B43)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" s="38">
         <f>SUMIF(Inventory!G2:G1000,B43,Inventory!E2:E1000)</f>
-        <v>4963</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="39">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C44" s="39">
         <f>COUNTIF(Inventory!G2:G1000,B44)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" s="40">
         <f>SUMIF(Inventory!G2:G1000,B44,Inventory!E2:E1000)</f>
-        <v>17807</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="37">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C45" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B45)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D45" s="38">
         <f>SUMIF(Inventory!G2:G1000,B45,Inventory!E2:E1000)</f>
+        <v>4963</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="39">
+        <v>2024</v>
+      </c>
+      <c r="C46" s="39">
+        <f>COUNTIF(Inventory!G2:G1000,B46)</f>
+        <v>11</v>
+      </c>
+      <c r="D46" s="40">
+        <f>SUMIF(Inventory!G2:G1000,B46,Inventory!E2:E1000)</f>
+        <v>17807</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="37">
+        <v>2025</v>
+      </c>
+      <c r="C47" s="37">
+        <f>COUNTIF(Inventory!G2:G1000,B47)</f>
+        <v>11</v>
+      </c>
+      <c r="D47" s="38">
+        <f>SUMIF(Inventory!G2:G1000,B47,Inventory!E2:E1000)</f>
         <v>12937</v>
       </c>
     </row>
-    <row r="46" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="41">
+    <row r="48" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="41">
         <v>2026</v>
       </c>
-      <c r="C46" s="41">
-        <f>COUNTIF(Inventory!G2:G1000,B46)</f>
+      <c r="C48" s="41">
+        <f>COUNTIF(Inventory!G2:G1000,B48)</f>
         <v>23</v>
       </c>
-      <c r="D46" s="42">
-        <f>SUMIF(Inventory!G2:G1000,B46,Inventory!E2:E1000)</f>
+      <c r="D48" s="42">
+        <f>SUMIF(Inventory!G2:G1000,B48,Inventory!E2:E1000)</f>
         <v>44701</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="28" t="s">
+    <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C49" s="28">
         <f>COUNTIF(Inventory!G2:G1000,"-")</f>
-        <v>52</v>
-      </c>
-      <c r="D47" s="43">
+        <v>56</v>
+      </c>
+      <c r="D49" s="43">
         <f>SUMIF(Inventory!G2:G1000,"-",Inventory!E2:E1000)</f>
-        <v>68767</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="44" t="s">
+        <v>71656</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="35">
-        <f>SUM(C35:C47)</f>
-        <v>137</v>
-      </c>
-      <c r="D48" s="45">
-        <f>SUM(D35:D47)</f>
-        <v>179757</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" ht="8.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" spans="2:15" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="111" t="s">
+      <c r="C50" s="35">
+        <f>SUM(C35:C49)</f>
+        <v>145</v>
+      </c>
+      <c r="D50" s="45">
+        <f>SUM(D35:D49)</f>
+        <v>184161</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="2:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="111"/>
-    </row>
-    <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-    </row>
-    <row r="52" spans="2:15" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
+      <c r="C52" s="86"/>
+      <c r="D52" s="86"/>
     </row>
     <row r="53" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
       <c r="E53" s="54"/>
       <c r="F53" s="55"/>
       <c r="G53" s="55"/>
@@ -10734,69 +10769,80 @@
       <c r="O53" s="55"/>
     </row>
     <row r="54" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="35" t="s">
-        <v>45</v>
-      </c>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
       <c r="E54" s="35" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="28">
+        <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="18">
+        <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B57" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="21">
+      <c r="C57" s="21">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>66</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="D57" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E55" s="28">
-        <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="11" t="s">
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B58" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C58" s="11">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>72</v>
-      </c>
-      <c r="D56" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="18" t="s">
         <v>14</v>
-      </c>
-      <c r="E56" s="18">
-        <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="F33:M33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="K34:M34"/>
-    <mergeCell ref="B10:O10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
     <mergeCell ref="L11:M11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
@@ -10810,21 +10856,22 @@
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="F33:M33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="B10:O10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="N11:O11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15164,16 +15211,30 @@
         <f t="shared" si="5"/>
         <v>139</v>
       </c>
-      <c r="B140" s="66"/>
-      <c r="C140" s="67"/>
-      <c r="D140" s="68"/>
-      <c r="E140" s="66"/>
-      <c r="F140" s="66"/>
-      <c r="G140" s="66"/>
-      <c r="H140" s="68"/>
+      <c r="B140" s="66">
+        <v>40926</v>
+      </c>
+      <c r="C140" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="D140" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="E140" s="66">
+        <v>479</v>
+      </c>
+      <c r="F140" s="66">
+        <v>2026</v>
+      </c>
+      <c r="G140" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="H140" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I140" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15181,16 +15242,30 @@
         <f t="shared" si="5"/>
         <v>140</v>
       </c>
-      <c r="B141" s="66"/>
-      <c r="C141" s="67"/>
-      <c r="D141" s="68"/>
-      <c r="E141" s="66"/>
-      <c r="F141" s="66"/>
-      <c r="G141" s="66"/>
-      <c r="H141" s="68"/>
+      <c r="B141" s="66">
+        <v>21368</v>
+      </c>
+      <c r="C141" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="D141" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E141" s="66">
+        <v>964</v>
+      </c>
+      <c r="F141" s="66">
+        <v>2026</v>
+      </c>
+      <c r="G141" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="H141" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I141" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15198,16 +15273,30 @@
         <f t="shared" si="5"/>
         <v>141</v>
       </c>
-      <c r="B142" s="66"/>
-      <c r="C142" s="67"/>
-      <c r="D142" s="68"/>
-      <c r="E142" s="66"/>
-      <c r="F142" s="66"/>
-      <c r="G142" s="66"/>
-      <c r="H142" s="68"/>
+      <c r="B142" s="66">
+        <v>77260</v>
+      </c>
+      <c r="C142" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="D142" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" s="66">
+        <v>292</v>
+      </c>
+      <c r="F142" s="66">
+        <v>2026</v>
+      </c>
+      <c r="G142" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="H142" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I142" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15215,16 +15304,30 @@
         <f t="shared" si="5"/>
         <v>142</v>
       </c>
-      <c r="B143" s="66"/>
-      <c r="C143" s="67"/>
-      <c r="D143" s="68"/>
-      <c r="E143" s="66"/>
-      <c r="F143" s="66"/>
-      <c r="G143" s="66"/>
-      <c r="H143" s="68"/>
+      <c r="B143" s="66">
+        <v>77985</v>
+      </c>
+      <c r="C143" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="D143" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E143" s="66">
+        <v>1154</v>
+      </c>
+      <c r="F143" s="66">
+        <v>2026</v>
+      </c>
+      <c r="G143" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="H143" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I143" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15232,16 +15335,30 @@
         <f t="shared" si="5"/>
         <v>143</v>
       </c>
-      <c r="B144" s="66"/>
-      <c r="C144" s="67"/>
-      <c r="D144" s="68"/>
-      <c r="E144" s="66"/>
-      <c r="F144" s="66"/>
-      <c r="G144" s="66"/>
-      <c r="H144" s="68"/>
+      <c r="B144" s="66">
+        <v>8007</v>
+      </c>
+      <c r="C144" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="D144" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E144" s="66">
+        <v>341</v>
+      </c>
+      <c r="F144" s="66">
+        <v>2001</v>
+      </c>
+      <c r="G144" s="66">
+        <v>2002</v>
+      </c>
+      <c r="H144" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I144" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Retired</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15249,16 +15366,30 @@
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="B145" s="66"/>
-      <c r="C145" s="67"/>
-      <c r="D145" s="68"/>
-      <c r="E145" s="66"/>
-      <c r="F145" s="66"/>
-      <c r="G145" s="66"/>
-      <c r="H145" s="68"/>
+      <c r="B145" s="66">
+        <v>8008</v>
+      </c>
+      <c r="C145" s="67" t="s">
+        <v>209</v>
+      </c>
+      <c r="D145" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E145" s="66">
+        <v>361</v>
+      </c>
+      <c r="F145" s="66">
+        <v>2001</v>
+      </c>
+      <c r="G145" s="66">
+        <v>2002</v>
+      </c>
+      <c r="H145" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I145" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Retired</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15266,16 +15397,30 @@
         <f t="shared" si="5"/>
         <v>145</v>
       </c>
-      <c r="B146" s="66"/>
-      <c r="C146" s="67"/>
-      <c r="D146" s="68"/>
-      <c r="E146" s="66"/>
-      <c r="F146" s="66"/>
-      <c r="G146" s="66"/>
-      <c r="H146" s="68"/>
+      <c r="B146" s="66">
+        <v>8010</v>
+      </c>
+      <c r="C146" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="D146" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="66">
+        <v>391</v>
+      </c>
+      <c r="F146" s="66">
+        <v>2002</v>
+      </c>
+      <c r="G146" s="66">
+        <v>2003</v>
+      </c>
+      <c r="H146" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I146" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Retired</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -15283,16 +15428,30 @@
         <f t="shared" si="5"/>
         <v>146</v>
       </c>
-      <c r="B147" s="66"/>
-      <c r="C147" s="67"/>
-      <c r="D147" s="68"/>
-      <c r="E147" s="66"/>
-      <c r="F147" s="66"/>
-      <c r="G147" s="66"/>
-      <c r="H147" s="68"/>
+      <c r="B147" s="66">
+        <v>8011</v>
+      </c>
+      <c r="C147" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D147" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" s="66">
+        <v>422</v>
+      </c>
+      <c r="F147" s="66">
+        <v>2002</v>
+      </c>
+      <c r="G147" s="66">
+        <v>2003</v>
+      </c>
+      <c r="H147" s="68" t="s">
+        <v>55</v>
+      </c>
       <c r="I147" s="66" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Retired</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BFA551-E222-4100-8F80-BC8127340E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DE96BB-D8E3-4749-A7EF-50801F4EAEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="210" windowWidth="19110" windowHeight="20110" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="390" windowWidth="19180" windowHeight="20020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="226">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -740,6 +740,9 @@
   <si>
     <t>Updated</t>
   </si>
+  <si>
+    <t>FIFA World Cup 2026 Official Emblem</t>
+  </si>
 </sst>
 </file>
 
@@ -747,7 +750,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-416]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-416]dd\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-416]dd\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="35" x14ac:knownFonts="1">
     <font>
@@ -1587,49 +1590,48 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1674,47 +1676,48 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2181,10 +2184,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>66</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>88</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2612,7 +2615,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>86</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>68</c:v>
@@ -3945,7 +3948,7 @@
                   <c:v>811</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7696</c:v>
+                  <c:v>7994</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1161</c:v>
@@ -5818,167 +5821,167 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98" t="s">
+      <c r="C4" s="134"/>
+      <c r="D4" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="98"/>
-      <c r="F4" s="99" t="s">
+      <c r="E4" s="134"/>
+      <c r="F4" s="135" t="s">
         <v>208</v>
       </c>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98" t="s">
+      <c r="G4" s="134"/>
+      <c r="H4" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="98"/>
-      <c r="J4" s="100" t="s">
+      <c r="I4" s="134"/>
+      <c r="J4" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="101"/>
-      <c r="L4" s="102"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="138"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="104">
+      <c r="B5" s="125">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>154</v>
-      </c>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105">
+        <v>155</v>
+      </c>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
-        <v>66</v>
-      </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106">
+        <v>69</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="127">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>88</v>
-      </c>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107">
+        <v>86</v>
+      </c>
+      <c r="G5" s="127"/>
+      <c r="H5" s="128">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>86</v>
-      </c>
-      <c r="I5" s="107"/>
-      <c r="J5" s="93">
+        <v>87</v>
+      </c>
+      <c r="I5" s="128"/>
+      <c r="J5" s="129">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>68</v>
       </c>
-      <c r="K5" s="94"/>
-      <c r="L5" s="95"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="131"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="103">
+      <c r="B6" s="110">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>194059</v>
-      </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103">
+        <v>194357</v>
+      </c>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
-        <v>76040</v>
-      </c>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103">
+        <v>77416</v>
+      </c>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>118019</v>
-      </c>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103">
+        <v>116941</v>
+      </c>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>123416</v>
-      </c>
-      <c r="I6" s="103"/>
-      <c r="J6" s="123">
+        <v>123714</v>
+      </c>
+      <c r="I6" s="110"/>
+      <c r="J6" s="95">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>70643</v>
       </c>
-      <c r="K6" s="124"/>
-      <c r="L6" s="125"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="97"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="55"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="133" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="132"/>
-      <c r="J7" s="126" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="K7" s="127"/>
-      <c r="L7" s="128"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="100"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="134"/>
-      <c r="C8" s="134"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="131"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="103"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="94" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
     </row>
     <row r="11" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
-      <c r="C11" s="109" t="s">
+      <c r="C11" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111" t="s">
+      <c r="D11" s="113"/>
+      <c r="E11" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="120" t="s">
+      <c r="F11" s="115"/>
+      <c r="G11" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="121"/>
+      <c r="H11" s="124"/>
     </row>
     <row r="12" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
@@ -6007,11 +6010,11 @@
       </c>
       <c r="C13" s="28">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Not Retired")</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D13" s="43">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Not Retired")</f>
-        <v>35388</v>
+        <v>36764</v>
       </c>
       <c r="E13" s="30">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
@@ -6023,11 +6026,11 @@
       </c>
       <c r="G13" s="74">
         <f ca="1">C13+E13</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H13" s="47">
         <f ca="1">D13+F13</f>
-        <v>76040</v>
+        <v>77416</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -6036,11 +6039,11 @@
       </c>
       <c r="C14" s="16">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="48">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>88028</v>
+        <v>86950</v>
       </c>
       <c r="E14" s="18">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
@@ -6052,11 +6055,11 @@
       </c>
       <c r="G14" s="75">
         <f ca="1">C14+E14</f>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H14" s="50">
         <f ca="1">D14+F14</f>
-        <v>118019</v>
+        <v>116941</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -6065,11 +6068,11 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" ref="C15:F15" ca="1" si="0">C13+C14</f>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>123416</v>
+        <v>123714</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -6081,62 +6084,62 @@
       </c>
       <c r="G15" s="76">
         <f ca="1">G13+G14</f>
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H15" s="33">
         <f ca="1">H13+H14</f>
-        <v>194059</v>
+        <v>194357</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="114"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="117"/>
+      <c r="N17" s="117"/>
+      <c r="O17" s="117"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="115"/>
-      <c r="C18" s="116" t="s">
+      <c r="B18" s="118"/>
+      <c r="C18" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="116"/>
-      <c r="E18" s="117" t="s">
+      <c r="D18" s="119"/>
+      <c r="E18" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="118" t="s">
+      <c r="F18" s="120"/>
+      <c r="G18" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="118"/>
-      <c r="I18" s="119" t="s">
+      <c r="H18" s="121"/>
+      <c r="I18" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="119"/>
+      <c r="J18" s="122"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="109" t="s">
+      <c r="L18" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="109"/>
-      <c r="N18" s="111" t="s">
+      <c r="M18" s="112"/>
+      <c r="N18" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="O18" s="111"/>
+      <c r="O18" s="114"/>
     </row>
     <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="115"/>
+      <c r="B19" s="118"/>
       <c r="C19" s="3" t="s">
         <v>14</v>
       </c>
@@ -6513,36 +6516,36 @@
       </c>
       <c r="E26" s="11">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B26,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="12">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B26,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>2472</v>
+        <v>2770</v>
       </c>
       <c r="G26" s="13">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" si="6"/>
-        <v>7696</v>
+        <v>7994</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="8"/>
-        <v>0.6787941787941788</v>
+        <v>0.65349011758819109</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="16">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B26,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M26" s="17">
         <f ca="1">SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B26,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>7696</v>
+        <v>7994</v>
       </c>
       <c r="N26" s="18">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B26,Inventory!$I$2:$I$1000,"Retired")</f>
@@ -6613,19 +6616,19 @@
       </c>
       <c r="C28" s="9">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B28,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="10">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B28,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>18844</v>
+        <v>19382</v>
       </c>
       <c r="E28" s="11">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B28,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" s="12">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B28,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>25217</v>
+        <v>24679</v>
       </c>
       <c r="G28" s="13">
         <f t="shared" si="5"/>
@@ -6637,11 +6640,11 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="7"/>
-        <v>0.47058823529411764</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="8"/>
-        <v>0.42767980753954743</v>
+        <v>0.43989015228887224</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="16">
@@ -6883,19 +6886,19 @@
       </c>
       <c r="C33" s="21">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B33,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="22">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B33,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="E33" s="23">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B33,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="24">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B33,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>2637</v>
+        <v>2050</v>
       </c>
       <c r="G33" s="25">
         <f t="shared" si="5"/>
@@ -6907,11 +6910,11 @@
       </c>
       <c r="I33" s="27">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J33" s="27">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.22260144103147517</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="28">
@@ -6991,19 +6994,19 @@
       </c>
       <c r="C35" s="21">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="22">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>1259</v>
+        <v>1510</v>
       </c>
       <c r="E35" s="23">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" s="24">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>1857</v>
+        <v>1606</v>
       </c>
       <c r="G35" s="25">
         <f t="shared" si="5"/>
@@ -7015,11 +7018,11 @@
       </c>
       <c r="I35" s="27">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" s="27">
         <f t="shared" si="8"/>
-        <v>0.40404364569961487</v>
+        <v>0.48459563543003853</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="28">
@@ -7207,44 +7210,44 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" ref="C39:H39" si="13">SUM(C20:C37)</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D39" s="33">
         <f t="shared" si="13"/>
-        <v>73004</v>
+        <v>74380</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="13"/>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" si="13"/>
-        <v>116503</v>
+        <v>115425</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="13"/>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H39" s="33">
         <f t="shared" si="13"/>
-        <v>189507</v>
+        <v>189805</v>
       </c>
       <c r="I39" s="34">
         <f t="shared" si="3"/>
-        <v>0.42384105960264901</v>
+        <v>0.44078947368421051</v>
       </c>
       <c r="J39" s="34">
         <f t="shared" si="4"/>
-        <v>0.38523115241125655</v>
+        <v>0.39187587260609574</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="1">
         <f ca="1">SUM(L20:L37)</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M39" s="33">
         <f ca="1">SUM(M20:M37)</f>
-        <v>121900</v>
+        <v>122198</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">SUM(N20:N37)</f>
@@ -7257,11 +7260,11 @@
     </row>
     <row r="40" spans="2:18" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="113"/>
-      <c r="D41" s="113"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="116"/>
       <c r="E41" s="54"/>
       <c r="N41" s="54"/>
       <c r="O41" s="54"/>
@@ -7478,11 +7481,11 @@
       </c>
       <c r="C57" s="28">
         <f>COUNTIF(Inventory!G2:G1000,"-")</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D57" s="43">
         <f>SUMIF(Inventory!G2:G1000,"-",Inventory!E2:E1000)</f>
-        <v>78715</v>
+        <v>79013</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>42</v>
@@ -7503,25 +7506,25 @@
       </c>
       <c r="C58" s="35">
         <f>SUM(C43:C57)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D58" s="45">
         <f>SUM(D43:D57)</f>
-        <v>193572</v>
+        <v>193870</v>
       </c>
       <c r="F58" s="21" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="21">
         <f ca="1">+G13</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H58" s="28" t="s">
         <v>12</v>
       </c>
       <c r="I58" s="28">
         <f ca="1">+C15</f>
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7530,7 +7533,7 @@
       </c>
       <c r="G59" s="11">
         <f ca="1">+G14</f>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>13</v>
@@ -7541,11 +7544,11 @@
       </c>
     </row>
     <row r="60" spans="2:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="108" t="s">
+      <c r="B60" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="108"/>
-      <c r="D60" s="108"/>
+      <c r="C60" s="111"/>
+      <c r="D60" s="111"/>
     </row>
     <row r="61" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="36"/>
@@ -7574,6 +7577,30 @@
     <sortCondition ref="B20:B38"/>
   </sortState>
   <mergeCells count="40">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
@@ -7589,31 +7616,7 @@
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:O17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G11:H11"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10201,7 +10204,7 @@
         <v>52</v>
       </c>
       <c r="H83" s="62" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I83" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10450,7 +10453,7 @@
         <v>2026</v>
       </c>
       <c r="H91" s="62" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I91" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10887,7 +10890,7 @@
         <v>52</v>
       </c>
       <c r="H105" s="62" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I105" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12449,16 +12452,30 @@
         <f t="shared" si="5"/>
         <v>155</v>
       </c>
-      <c r="B156" s="79"/>
-      <c r="C156" s="61"/>
-      <c r="D156" s="62"/>
-      <c r="E156" s="60"/>
-      <c r="F156" s="60"/>
-      <c r="G156" s="60"/>
-      <c r="H156" s="62"/>
+      <c r="B156" s="79">
+        <v>43032</v>
+      </c>
+      <c r="C156" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="D156" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="E156" s="60">
+        <v>298</v>
+      </c>
+      <c r="F156" s="60">
+        <v>2026</v>
+      </c>
+      <c r="G156" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="H156" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I156" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -21422,9 +21439,9 @@
       <c r="A1" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="138">
+      <c r="B1" s="93">
         <f ca="1">+TODAY()</f>
-        <v>46206</v>
+        <v>46211</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -1591,47 +1591,46 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1676,46 +1675,47 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5821,167 +5821,167 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="94" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="133"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="134" t="s">
+      <c r="B4" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="134"/>
-      <c r="D4" s="134" t="s">
+      <c r="C4" s="96"/>
+      <c r="D4" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="134"/>
-      <c r="F4" s="135" t="s">
+      <c r="E4" s="96"/>
+      <c r="F4" s="97" t="s">
         <v>208</v>
       </c>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134" t="s">
+      <c r="G4" s="96"/>
+      <c r="H4" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="134"/>
-      <c r="J4" s="136" t="s">
+      <c r="I4" s="96"/>
+      <c r="J4" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="137"/>
-      <c r="L4" s="138"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="100"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="125">
+      <c r="B5" s="101">
         <f>COUNTA(Inventory!C2:C1000)</f>
         <v>155</v>
       </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="126">
+      <c r="C5" s="101"/>
+      <c r="D5" s="102">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
         <v>69</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="127">
+      <c r="E5" s="102"/>
+      <c r="F5" s="103">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
         <v>86</v>
       </c>
-      <c r="G5" s="127"/>
-      <c r="H5" s="128">
+      <c r="G5" s="103"/>
+      <c r="H5" s="104">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
         <v>87</v>
       </c>
-      <c r="I5" s="128"/>
-      <c r="J5" s="129">
+      <c r="I5" s="104"/>
+      <c r="J5" s="105">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
         <v>68</v>
       </c>
-      <c r="K5" s="130"/>
-      <c r="L5" s="131"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="107"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="110">
+      <c r="B6" s="138">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
         <v>194357</v>
       </c>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110">
+      <c r="C6" s="138"/>
+      <c r="D6" s="138">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
         <v>77416</v>
       </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110">
+      <c r="E6" s="138"/>
+      <c r="F6" s="138">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
         <v>116941</v>
       </c>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110">
+      <c r="G6" s="138"/>
+      <c r="H6" s="138">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
         <v>123714</v>
       </c>
-      <c r="I6" s="110"/>
-      <c r="J6" s="95">
+      <c r="I6" s="138"/>
+      <c r="J6" s="123">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
         <v>70643</v>
       </c>
-      <c r="K6" s="96"/>
-      <c r="L6" s="97"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="125"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="55"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="132" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="105" t="s">
+      <c r="E7" s="132"/>
+      <c r="F7" s="133" t="s">
         <v>164</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104" t="s">
+      <c r="G7" s="132"/>
+      <c r="H7" s="132" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="104"/>
-      <c r="J7" s="98" t="s">
+      <c r="I7" s="132"/>
+      <c r="J7" s="126" t="s">
         <v>165</v>
       </c>
-      <c r="K7" s="99"/>
-      <c r="L7" s="100"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="128"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="106"/>
-      <c r="C8" s="106"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="101"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="103"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="136"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="129"/>
+      <c r="K8" s="130"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="122"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="122"/>
+      <c r="H10" s="122"/>
     </row>
     <row r="11" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
-      <c r="C11" s="112" t="s">
+      <c r="C11" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="113"/>
-      <c r="E11" s="114" t="s">
+      <c r="D11" s="110"/>
+      <c r="E11" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="115"/>
-      <c r="G11" s="123" t="s">
+      <c r="F11" s="112"/>
+      <c r="G11" s="120" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="124"/>
+      <c r="H11" s="121"/>
     </row>
     <row r="12" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
@@ -6093,53 +6093,53 @@
     </row>
     <row r="16" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="117" t="s">
+      <c r="B17" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="114"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="118"/>
-      <c r="C18" s="119" t="s">
+      <c r="B18" s="115"/>
+      <c r="C18" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="119"/>
-      <c r="E18" s="120" t="s">
+      <c r="D18" s="116"/>
+      <c r="E18" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121" t="s">
+      <c r="F18" s="117"/>
+      <c r="G18" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="121"/>
-      <c r="I18" s="122" t="s">
+      <c r="H18" s="118"/>
+      <c r="I18" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="122"/>
+      <c r="J18" s="119"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="112" t="s">
+      <c r="L18" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="112"/>
-      <c r="N18" s="114" t="s">
+      <c r="M18" s="109"/>
+      <c r="N18" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="O18" s="114"/>
+      <c r="O18" s="111"/>
     </row>
     <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="118"/>
+      <c r="B19" s="115"/>
       <c r="C19" s="3" t="s">
         <v>14</v>
       </c>
@@ -7260,11 +7260,11 @@
     </row>
     <row r="40" spans="2:18" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="116" t="s">
+      <c r="B41" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="116"/>
-      <c r="D41" s="116"/>
+      <c r="C41" s="113"/>
+      <c r="D41" s="113"/>
       <c r="E41" s="54"/>
       <c r="N41" s="54"/>
       <c r="O41" s="54"/>
@@ -7544,11 +7544,11 @@
       </c>
     </row>
     <row r="60" spans="2:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="111" t="s">
+      <c r="B60" s="108" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="111"/>
-      <c r="D60" s="111"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="108"/>
     </row>
     <row r="61" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="36"/>
@@ -7577,30 +7577,6 @@
     <sortCondition ref="B20:B38"/>
   </sortState>
   <mergeCells count="40">
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:O17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G11:H11"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
@@ -7617,6 +7593,30 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DE96BB-D8E3-4749-A7EF-50801F4EAEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE51B287-2D58-4AEA-A6A8-9226635FD7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="390" windowWidth="19180" windowHeight="20020" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="235">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -742,6 +742,33 @@
   </si>
   <si>
     <t>FIFA World Cup 2026 Official Emblem</t>
+  </si>
+  <si>
+    <t>McLaren F1 Team MCL38</t>
+  </si>
+  <si>
+    <t>Williams Racing FW46</t>
+  </si>
+  <si>
+    <t>Visa Cash App VCARB 01</t>
+  </si>
+  <si>
+    <t>Aston Martin Aramco F1</t>
+  </si>
+  <si>
+    <t>MoneyGram Haas F1 Team VF-24</t>
+  </si>
+  <si>
+    <t>BWT Alpine F1 Team</t>
+  </si>
+  <si>
+    <t>KICK Sauber F1 Team C44</t>
+  </si>
+  <si>
+    <t>Mercedes-AMG F1 W12 E Performance &amp; Mercedes-AMG Project</t>
+  </si>
+  <si>
+    <t>2023 McLaren Formula 1 Car</t>
   </si>
 </sst>
 </file>
@@ -1591,46 +1618,47 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1675,47 +1703,46 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2184,10 +2211,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>69</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>86</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2615,10 +2642,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>87</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>68</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3975,7 +4002,7 @@
                   <c:v>1403</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3116</c:v>
+                  <c:v>5733</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>50958</c:v>
@@ -5821,167 +5848,167 @@
   <sheetData>
     <row r="1" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="132" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="133"/>
     </row>
     <row r="3" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96" t="s">
+      <c r="C4" s="134"/>
+      <c r="D4" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="96"/>
-      <c r="F4" s="97" t="s">
+      <c r="E4" s="134"/>
+      <c r="F4" s="135" t="s">
         <v>208</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96" t="s">
+      <c r="G4" s="134"/>
+      <c r="H4" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="96"/>
-      <c r="J4" s="98" t="s">
+      <c r="I4" s="134"/>
+      <c r="J4" s="136" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="99"/>
-      <c r="L4" s="100"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="138"/>
     </row>
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
-      <c r="B5" s="101">
+      <c r="B5" s="125">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>155</v>
-      </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="102">
+        <v>164</v>
+      </c>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126">
         <f>COUNTIF(Inventory!H2:H1000,"YES")</f>
-        <v>69</v>
-      </c>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103">
+        <v>71</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="127">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>86</v>
-      </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="104">
+        <v>93</v>
+      </c>
+      <c r="G5" s="127"/>
+      <c r="H5" s="128">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>87</v>
-      </c>
-      <c r="I5" s="104"/>
-      <c r="J5" s="105">
+        <v>93</v>
+      </c>
+      <c r="I5" s="128"/>
+      <c r="J5" s="129">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
-        <v>68</v>
-      </c>
-      <c r="K5" s="106"/>
-      <c r="L5" s="107"/>
+        <v>71</v>
+      </c>
+      <c r="K5" s="130"/>
+      <c r="L5" s="131"/>
     </row>
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="138">
+      <c r="B6" s="110">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>194357</v>
-      </c>
-      <c r="C6" s="138"/>
-      <c r="D6" s="138">
+        <v>196974</v>
+      </c>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110">
         <f>SUMIF(Inventory!H2:H1000,"YES",Inventory!E2:E1000)</f>
-        <v>77416</v>
-      </c>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138">
+        <v>77898</v>
+      </c>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>116941</v>
-      </c>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138">
+        <v>119076</v>
+      </c>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>123714</v>
-      </c>
-      <c r="I6" s="138"/>
-      <c r="J6" s="123">
+        <v>125263</v>
+      </c>
+      <c r="I6" s="110"/>
+      <c r="J6" s="95">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
-        <v>70643</v>
-      </c>
-      <c r="K6" s="124"/>
-      <c r="L6" s="125"/>
+        <v>71711</v>
+      </c>
+      <c r="K6" s="96"/>
+      <c r="L6" s="97"/>
       <c r="Q6" s="51"/>
       <c r="R6" s="55"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="133" t="s">
+      <c r="E7" s="104"/>
+      <c r="F7" s="105" t="s">
         <v>164</v>
       </c>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="132"/>
-      <c r="J7" s="126" t="s">
+      <c r="I7" s="104"/>
+      <c r="J7" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="K7" s="127"/>
-      <c r="L7" s="128"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="100"/>
     </row>
     <row r="8" spans="2:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="134"/>
-      <c r="C8" s="134"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="129"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="131"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="103"/>
     </row>
     <row r="9" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="94" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
     </row>
     <row r="11" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
-      <c r="C11" s="109" t="s">
+      <c r="C11" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111" t="s">
+      <c r="D11" s="113"/>
+      <c r="E11" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="112"/>
-      <c r="G11" s="120" t="s">
+      <c r="F11" s="115"/>
+      <c r="G11" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="121"/>
+      <c r="H11" s="124"/>
     </row>
     <row r="12" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
@@ -6010,11 +6037,11 @@
       </c>
       <c r="C13" s="28">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Not Retired")</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="43">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Not Retired")</f>
-        <v>36764</v>
+        <v>37246</v>
       </c>
       <c r="E13" s="30">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"YES",Inventory!I2:I1000,"Retired")</f>
@@ -6026,11 +6053,11 @@
       </c>
       <c r="G13" s="74">
         <f ca="1">C13+E13</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H13" s="47">
         <f ca="1">D13+F13</f>
-        <v>77416</v>
+        <v>77898</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -6039,27 +6066,27 @@
       </c>
       <c r="C14" s="16">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D14" s="48">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>86950</v>
+        <v>88017</v>
       </c>
       <c r="E14" s="18">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F14" s="49">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
-        <v>29991</v>
+        <v>31059</v>
       </c>
       <c r="G14" s="75">
         <f ca="1">C14+E14</f>
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H14" s="50">
         <f ca="1">D14+F14</f>
-        <v>116941</v>
+        <v>119076</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -6068,78 +6095,78 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" ref="C15:F15" ca="1" si="0">C13+C14</f>
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D15" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>123714</v>
+        <v>125263</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>70643</v>
+        <v>71711</v>
       </c>
       <c r="G15" s="76">
         <f ca="1">G13+G14</f>
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H15" s="33">
         <f ca="1">H13+H14</f>
-        <v>194357</v>
+        <v>196974</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="114"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
+      <c r="K17" s="117"/>
+      <c r="L17" s="117"/>
+      <c r="M17" s="117"/>
+      <c r="N17" s="117"/>
+      <c r="O17" s="117"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="115"/>
-      <c r="C18" s="116" t="s">
+      <c r="B18" s="118"/>
+      <c r="C18" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="116"/>
-      <c r="E18" s="117" t="s">
+      <c r="D18" s="119"/>
+      <c r="E18" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="117"/>
-      <c r="G18" s="118" t="s">
+      <c r="F18" s="120"/>
+      <c r="G18" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="118"/>
-      <c r="I18" s="119" t="s">
+      <c r="H18" s="121"/>
+      <c r="I18" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="119"/>
+      <c r="J18" s="122"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="109" t="s">
+      <c r="L18" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="M18" s="109"/>
-      <c r="N18" s="111" t="s">
+      <c r="M18" s="112"/>
+      <c r="N18" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="O18" s="111"/>
+      <c r="O18" s="114"/>
     </row>
     <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="115"/>
+      <c r="B19" s="118"/>
       <c r="C19" s="3" t="s">
         <v>14</v>
       </c>
@@ -6994,52 +7021,52 @@
       </c>
       <c r="C35" s="21">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="22">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"YES")</f>
-        <v>1510</v>
+        <v>1992</v>
       </c>
       <c r="E35" s="23">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F35" s="24">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B35,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>1606</v>
+        <v>3741</v>
       </c>
       <c r="G35" s="25">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H35" s="26">
         <f t="shared" si="6"/>
-        <v>3116</v>
+        <v>5733</v>
       </c>
       <c r="I35" s="27">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0.36842105263157893</v>
       </c>
       <c r="J35" s="27">
         <f t="shared" si="8"/>
-        <v>0.48459563543003853</v>
+        <v>0.34746206174777605</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="28">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B35,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M35" s="29">
         <f ca="1">SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B35,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>2552</v>
+        <v>4101</v>
       </c>
       <c r="N35" s="30">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B35,Inventory!$I$2:$I$1000,"Retired")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O35" s="31">
         <f ca="1">SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B35,Inventory!$I$2:$I$1000,"Retired")</f>
-        <v>564</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="36" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7210,61 +7237,61 @@
       </c>
       <c r="C39" s="1">
         <f t="shared" ref="C39:H39" si="13">SUM(C20:C37)</f>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D39" s="33">
         <f t="shared" si="13"/>
-        <v>74380</v>
+        <v>74862</v>
       </c>
       <c r="E39" s="1">
         <f t="shared" si="13"/>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" si="13"/>
-        <v>115425</v>
+        <v>117560</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="13"/>
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H39" s="33">
         <f t="shared" si="13"/>
-        <v>189805</v>
+        <v>192422</v>
       </c>
       <c r="I39" s="34">
         <f t="shared" si="3"/>
-        <v>0.44078947368421051</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="J39" s="34">
         <f t="shared" si="4"/>
-        <v>0.39187587260609574</v>
+        <v>0.38905114799763019</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="1">
         <f ca="1">SUM(L20:L37)</f>
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M39" s="33">
         <f ca="1">SUM(M20:M37)</f>
-        <v>122198</v>
+        <v>123747</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">SUM(N20:N37)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O39" s="33">
         <f ca="1">SUM(O20:O37)</f>
-        <v>67607</v>
+        <v>68675</v>
       </c>
     </row>
     <row r="40" spans="2:18" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="113"/>
-      <c r="D41" s="113"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="116"/>
       <c r="E41" s="54"/>
       <c r="N41" s="54"/>
       <c r="O41" s="54"/>
@@ -7436,11 +7463,11 @@
       </c>
       <c r="C54" s="39">
         <f>COUNTIF(Inventory!G2:G1000,B54)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" s="40">
         <f>SUMIF(Inventory!G2:G1000,B54,Inventory!E2:E1000)</f>
-        <v>20159</v>
+        <v>20723</v>
       </c>
     </row>
     <row r="55" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7449,11 +7476,11 @@
       </c>
       <c r="C55" s="37">
         <f>COUNTIF(Inventory!G2:G1000,B55)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D55" s="38">
         <f>SUMIF(Inventory!G2:G1000,B55,Inventory!E2:E1000)</f>
-        <v>12937</v>
+        <v>13441</v>
       </c>
     </row>
     <row r="56" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7462,11 +7489,11 @@
       </c>
       <c r="C56" s="41">
         <f>COUNTIF(Inventory!G2:G1000,B56)</f>
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D56" s="42">
         <f>SUMIF(Inventory!G2:G1000,B56,Inventory!E2:E1000)</f>
-        <v>44701</v>
+        <v>46250</v>
       </c>
       <c r="F56" s="53" t="s">
         <v>41</v>
@@ -7506,25 +7533,25 @@
       </c>
       <c r="C58" s="35">
         <f>SUM(C43:C57)</f>
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D58" s="45">
         <f>SUM(D43:D57)</f>
-        <v>193870</v>
+        <v>196487</v>
       </c>
       <c r="F58" s="21" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="21">
         <f ca="1">+G13</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H58" s="28" t="s">
         <v>12</v>
       </c>
       <c r="I58" s="28">
         <f ca="1">+C15</f>
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7533,22 +7560,22 @@
       </c>
       <c r="G59" s="11">
         <f ca="1">+G14</f>
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>13</v>
       </c>
       <c r="I59" s="18">
         <f ca="1">+E15</f>
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="2:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="108" t="s">
+      <c r="B60" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="108"/>
-      <c r="D60" s="108"/>
+      <c r="C60" s="111"/>
+      <c r="D60" s="111"/>
     </row>
     <row r="61" spans="2:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="36"/>
@@ -7577,6 +7604,30 @@
     <sortCondition ref="B20:B38"/>
   </sortState>
   <mergeCells count="40">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G11:H11"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="J7:L7"/>
@@ -7593,30 +7644,6 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B17:O17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -10485,7 +10512,7 @@
         <v>2026</v>
       </c>
       <c r="H92" s="62" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I92" s="60" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11114,7 +11141,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="62">
         <f t="shared" si="3"/>
         <v>112</v>
@@ -11145,7 +11172,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="62">
         <f t="shared" si="3"/>
         <v>113</v>
@@ -11176,7 +11203,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="62">
         <f t="shared" si="3"/>
         <v>114</v>
@@ -11207,7 +11234,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="62">
         <f t="shared" si="3"/>
         <v>115</v>
@@ -11237,8 +11264,9 @@
         <f t="shared" ca="1" si="2"/>
         <v>Retired</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J116" s="56"/>
+    </row>
+    <row r="117" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="62">
         <f t="shared" si="3"/>
         <v>116</v>
@@ -11269,7 +11297,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="62">
         <f t="shared" si="3"/>
         <v>117</v>
@@ -11300,7 +11328,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="62">
         <f t="shared" si="3"/>
         <v>118</v>
@@ -11331,7 +11359,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="62">
         <f t="shared" si="3"/>
         <v>119</v>
@@ -11362,7 +11390,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="62">
         <f t="shared" si="3"/>
         <v>120</v>
@@ -11393,7 +11421,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="62">
         <f t="shared" si="3"/>
         <v>121</v>
@@ -11424,7 +11452,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="62">
         <f t="shared" si="3"/>
         <v>122</v>
@@ -11455,7 +11483,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="62">
         <f t="shared" si="3"/>
         <v>123</v>
@@ -11486,7 +11514,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="62">
         <f t="shared" si="3"/>
         <v>124</v>
@@ -11517,7 +11545,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="62">
         <f t="shared" si="3"/>
         <v>125</v>
@@ -11548,7 +11576,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="62">
         <f t="shared" si="3"/>
         <v>126</v>
@@ -11579,7 +11607,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="62">
         <f t="shared" si="3"/>
         <v>127</v>
@@ -11610,7 +11638,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="62">
         <f t="shared" si="3"/>
         <v>128</v>
@@ -11641,7 +11669,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="62">
         <f t="shared" si="3"/>
         <v>129</v>
@@ -11672,7 +11700,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="62">
         <f t="shared" ref="A131:A194" si="5">+A130+1</f>
         <v>130</v>
@@ -11703,7 +11731,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="62">
         <f t="shared" si="5"/>
         <v>131</v>
@@ -11734,7 +11762,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="62">
         <f t="shared" si="5"/>
         <v>132</v>
@@ -11765,7 +11793,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="62">
         <f t="shared" si="5"/>
         <v>133</v>
@@ -11796,7 +11824,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="62">
         <f t="shared" si="5"/>
         <v>134</v>
@@ -11820,14 +11848,15 @@
         <v>52</v>
       </c>
       <c r="H135" s="62" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I135" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>Not Retired</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J135" s="56"/>
+    </row>
+    <row r="136" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="62">
         <f t="shared" si="5"/>
         <v>135</v>
@@ -11858,7 +11887,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="62">
         <f t="shared" si="5"/>
         <v>136</v>
@@ -11889,7 +11918,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="62">
         <f t="shared" si="5"/>
         <v>137</v>
@@ -11920,7 +11949,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="62">
         <f t="shared" si="5"/>
         <v>138</v>
@@ -11951,7 +11980,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="62">
         <f t="shared" si="5"/>
         <v>139</v>
@@ -11982,7 +12011,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="62">
         <f t="shared" si="5"/>
         <v>140</v>
@@ -12013,7 +12042,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="62">
         <f t="shared" si="5"/>
         <v>141</v>
@@ -12044,7 +12073,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="62">
         <f t="shared" si="5"/>
         <v>142</v>
@@ -12075,7 +12104,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="62">
         <f t="shared" si="5"/>
         <v>143</v>
@@ -12106,7 +12135,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="62">
         <f t="shared" si="5"/>
         <v>144</v>
@@ -12137,7 +12166,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="62">
         <f t="shared" si="5"/>
         <v>145</v>
@@ -12168,7 +12197,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="62">
         <f t="shared" si="5"/>
         <v>146</v>
@@ -12199,7 +12228,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="62">
         <f t="shared" si="5"/>
         <v>147</v>
@@ -12230,7 +12259,7 @@
         <v>Retired</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="62">
         <f t="shared" si="5"/>
         <v>148</v>
@@ -12261,7 +12290,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="62">
         <f t="shared" si="5"/>
         <v>149</v>
@@ -12292,7 +12321,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="62">
         <f t="shared" si="5"/>
         <v>150</v>
@@ -12323,7 +12352,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="62">
         <f t="shared" si="5"/>
         <v>151</v>
@@ -12354,7 +12383,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="62">
         <f t="shared" si="5"/>
         <v>152</v>
@@ -12385,7 +12414,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="62">
         <f t="shared" si="5"/>
         <v>153</v>
@@ -12416,7 +12445,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="62">
         <f t="shared" si="5"/>
         <v>154</v>
@@ -12447,7 +12476,7 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="62">
         <f t="shared" si="5"/>
         <v>155</v>
@@ -12478,160 +12507,291 @@
         <v>Not Retired</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="62">
         <f t="shared" si="5"/>
         <v>156</v>
       </c>
-      <c r="B157" s="79"/>
-      <c r="C157" s="61"/>
-      <c r="D157" s="62"/>
-      <c r="E157" s="60"/>
-      <c r="F157" s="60"/>
-      <c r="G157" s="60"/>
-      <c r="H157" s="62"/>
+      <c r="B157" s="79">
+        <v>77251</v>
+      </c>
+      <c r="C157" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="D157" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E157" s="60">
+        <v>269</v>
+      </c>
+      <c r="F157" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G157" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H157" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I157" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Not Retired</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="62">
         <f t="shared" si="5"/>
         <v>157</v>
       </c>
-      <c r="B158" s="79"/>
-      <c r="C158" s="61"/>
-      <c r="D158" s="62"/>
-      <c r="E158" s="60"/>
-      <c r="F158" s="60"/>
-      <c r="G158" s="60"/>
-      <c r="H158" s="62"/>
+      <c r="B158" s="79">
+        <v>77249</v>
+      </c>
+      <c r="C158" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="D158" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158" s="60">
+        <v>263</v>
+      </c>
+      <c r="F158" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G158" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H158" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I158" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Not Retired</v>
+      </c>
+      <c r="J158" s="56"/>
+    </row>
+    <row r="159" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="62">
         <f t="shared" si="5"/>
         <v>158</v>
       </c>
-      <c r="B159" s="79"/>
-      <c r="C159" s="61"/>
-      <c r="D159" s="62"/>
-      <c r="E159" s="60"/>
-      <c r="F159" s="60"/>
-      <c r="G159" s="60"/>
-      <c r="H159" s="62"/>
+      <c r="B159" s="79">
+        <v>77246</v>
+      </c>
+      <c r="C159" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="D159" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" s="60">
+        <v>248</v>
+      </c>
+      <c r="F159" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G159" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H159" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I159" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Not Retired</v>
+      </c>
+      <c r="J159" s="56"/>
+    </row>
+    <row r="160" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="62">
         <f t="shared" si="5"/>
         <v>159</v>
       </c>
-      <c r="B160" s="79"/>
-      <c r="C160" s="61"/>
-      <c r="D160" s="62"/>
-      <c r="E160" s="60"/>
-      <c r="F160" s="60"/>
-      <c r="G160" s="60"/>
-      <c r="H160" s="62"/>
+      <c r="B160" s="79">
+        <v>77245</v>
+      </c>
+      <c r="C160" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="D160" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E160" s="60">
+        <v>269</v>
+      </c>
+      <c r="F160" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G160" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H160" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I160" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Not Retired</v>
+      </c>
+      <c r="J160" s="56"/>
+    </row>
+    <row r="161" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="62">
         <f t="shared" si="5"/>
         <v>160</v>
       </c>
-      <c r="B161" s="79"/>
-      <c r="C161" s="61"/>
-      <c r="D161" s="62"/>
-      <c r="E161" s="60"/>
-      <c r="F161" s="60"/>
-      <c r="G161" s="60"/>
-      <c r="H161" s="62"/>
+      <c r="B161" s="79">
+        <v>77250</v>
+      </c>
+      <c r="C161" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D161" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E161" s="60">
+        <v>242</v>
+      </c>
+      <c r="F161" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G161" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H161" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I161" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Not Retired</v>
+      </c>
+      <c r="J161" s="56"/>
+    </row>
+    <row r="162" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="62">
         <f t="shared" si="5"/>
         <v>161</v>
       </c>
-      <c r="B162" s="79"/>
-      <c r="C162" s="61"/>
-      <c r="D162" s="62"/>
-      <c r="E162" s="60"/>
-      <c r="F162" s="60"/>
-      <c r="G162" s="60"/>
-      <c r="H162" s="62"/>
+      <c r="B162" s="79">
+        <v>77248</v>
+      </c>
+      <c r="C162" s="61" t="s">
+        <v>231</v>
+      </c>
+      <c r="D162" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E162" s="60">
+        <v>258</v>
+      </c>
+      <c r="F162" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G162" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H162" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I162" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Not Retired</v>
+      </c>
+      <c r="J162" s="56"/>
+    </row>
+    <row r="163" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="62">
         <f t="shared" si="5"/>
         <v>162</v>
       </c>
-      <c r="B163" s="79"/>
-      <c r="C163" s="61"/>
-      <c r="D163" s="62"/>
-      <c r="E163" s="60"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="62"/>
+      <c r="B163" s="79">
+        <v>77247</v>
+      </c>
+      <c r="C163" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="D163" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E163" s="60">
+        <v>259</v>
+      </c>
+      <c r="F163" s="60">
+        <v>2025</v>
+      </c>
+      <c r="G163" s="60">
+        <v>2025</v>
+      </c>
+      <c r="H163" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I163" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Retired</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="62">
         <f t="shared" si="5"/>
         <v>163</v>
       </c>
-      <c r="B164" s="79"/>
-      <c r="C164" s="61"/>
-      <c r="D164" s="62"/>
-      <c r="E164" s="60"/>
-      <c r="F164" s="60"/>
-      <c r="G164" s="60"/>
-      <c r="H164" s="62"/>
+      <c r="B164" s="79">
+        <v>76919</v>
+      </c>
+      <c r="C164" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="D164" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E164" s="60">
+        <v>245</v>
+      </c>
+      <c r="F164" s="60">
+        <v>2024</v>
+      </c>
+      <c r="G164" s="60">
+        <v>2025</v>
+      </c>
+      <c r="H164" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I164" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Retired</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="62">
         <f t="shared" si="5"/>
         <v>164</v>
       </c>
-      <c r="B165" s="79"/>
-      <c r="C165" s="61"/>
-      <c r="D165" s="62"/>
-      <c r="E165" s="60"/>
-      <c r="F165" s="60"/>
-      <c r="G165" s="60"/>
-      <c r="H165" s="62"/>
+      <c r="B165" s="79">
+        <v>76909</v>
+      </c>
+      <c r="C165" s="61" t="s">
+        <v>233</v>
+      </c>
+      <c r="D165" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E165" s="60">
+        <v>564</v>
+      </c>
+      <c r="F165" s="60">
+        <v>2022</v>
+      </c>
+      <c r="G165" s="60">
+        <v>2024</v>
+      </c>
+      <c r="H165" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I165" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Retired</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="62">
         <f t="shared" si="5"/>
         <v>165</v>
@@ -12648,7 +12808,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="62">
         <f t="shared" si="5"/>
         <v>166</v>
@@ -12665,7 +12825,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="62">
         <f t="shared" si="5"/>
         <v>167</v>
@@ -12682,7 +12842,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="62">
         <f t="shared" si="5"/>
         <v>168</v>
@@ -12699,7 +12859,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="62">
         <f t="shared" si="5"/>
         <v>169</v>
@@ -12716,7 +12876,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="62">
         <f t="shared" si="5"/>
         <v>170</v>
@@ -12733,7 +12893,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="62">
         <f t="shared" si="5"/>
         <v>171</v>
@@ -12750,7 +12910,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="62">
         <f t="shared" si="5"/>
         <v>172</v>
@@ -12767,7 +12927,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="62">
         <f t="shared" si="5"/>
         <v>173</v>
@@ -12784,7 +12944,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="62">
         <f t="shared" si="5"/>
         <v>174</v>
@@ -12801,7 +12961,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="62">
         <f t="shared" si="5"/>
         <v>175</v>
@@ -21441,7 +21601,7 @@
       </c>
       <c r="B1" s="93">
         <f ca="1">+TODAY()</f>
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
   </sheetData>

--- a/data/LEGO_Dash.xlsx
+++ b/data/LEGO_Dash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfran\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE51B287-2D58-4AEA-A6A8-9226635FD7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E081E255-1C3E-4B7A-B9DC-C91EEC93A07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="390" windowWidth="19180" windowHeight="20020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="238">
   <si>
     <t>TOTAL SETS</t>
   </si>
@@ -769,6 +769,15 @@
   </si>
   <si>
     <t>2023 McLaren Formula 1 Car</t>
+  </si>
+  <si>
+    <t>Penguins in Love</t>
+  </si>
+  <si>
+    <t>Super Mario World™: Mario &amp; Yoshi</t>
+  </si>
+  <si>
+    <t>Super Mario 64 Question Mark Block</t>
   </si>
 </sst>
 </file>
@@ -2214,7 +2223,7 @@
                   <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93</c:v>
+                  <c:v>96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2642,10 +2651,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>93</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3993,7 +4002,7 @@
                   <c:v>6348</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8700</c:v>
+                  <c:v>8978</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2637</c:v>
@@ -4008,7 +4017,7 @@
                   <c:v>50958</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10854</c:v>
+                  <c:v>14133</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>4552</c:v>
@@ -5892,7 +5901,7 @@
     <row r="5" spans="2:18" ht="31" x14ac:dyDescent="0.35">
       <c r="B5" s="125">
         <f>COUNTA(Inventory!C2:C1000)</f>
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C5" s="125"/>
       <c r="D5" s="126">
@@ -5902,17 +5911,17 @@
       <c r="E5" s="126"/>
       <c r="F5" s="127">
         <f>COUNTIF(Inventory!H2:H1000,"NO")</f>
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G5" s="127"/>
       <c r="H5" s="128">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Not Retired")</f>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I5" s="128"/>
       <c r="J5" s="129">
         <f ca="1">COUNTIF(Inventory!I2:I1000,"Retired")</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" s="130"/>
       <c r="L5" s="131"/>
@@ -5920,7 +5929,7 @@
     <row r="6" spans="2:18" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="110">
         <f>SUMIF(Inventory!E2:E1000,"&lt;&gt;"&amp;"",Inventory!E2:E1000)</f>
-        <v>196974</v>
+        <v>200531</v>
       </c>
       <c r="C6" s="110"/>
       <c r="D6" s="110">
@@ -5930,17 +5939,17 @@
       <c r="E6" s="110"/>
       <c r="F6" s="110">
         <f>SUMIF(Inventory!H2:H1000,"NO",Inventory!E2:E1000)</f>
-        <v>119076</v>
+        <v>122633</v>
       </c>
       <c r="G6" s="110"/>
       <c r="H6" s="110">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Not Retired")</f>
-        <v>125263</v>
+        <v>126756</v>
       </c>
       <c r="I6" s="110"/>
       <c r="J6" s="95">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!I2:I1000,"Retired")</f>
-        <v>71711</v>
+        <v>73775</v>
       </c>
       <c r="K6" s="96"/>
       <c r="L6" s="97"/>
@@ -6066,27 +6075,27 @@
       </c>
       <c r="C14" s="16">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D14" s="48">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Not Retired")</f>
-        <v>88017</v>
+        <v>89510</v>
       </c>
       <c r="E14" s="18">
         <f ca="1">COUNTIFS(Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="49">
         <f ca="1">SUMIFS(Inventory!E2:E1000,Inventory!H2:H1000,"NO",Inventory!I2:I1000,"Retired")</f>
-        <v>31059</v>
+        <v>33123</v>
       </c>
       <c r="G14" s="75">
         <f ca="1">C14+E14</f>
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H14" s="50">
         <f ca="1">D14+F14</f>
-        <v>119076</v>
+        <v>122633</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -6095,27 +6104,27 @@
       </c>
       <c r="C15" s="1">
         <f t="shared" ref="C15:F15" ca="1" si="0">C13+C14</f>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D15" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>125263</v>
+        <v>126756</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>71711</v>
+        <v>73775</v>
       </c>
       <c r="G15" s="76">
         <f ca="1">G13+G14</f>
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H15" s="33">
         <f ca="1">H13+H14</f>
-        <v>196974</v>
+        <v>200531</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -6867,36 +6876,36 @@
       </c>
       <c r="E32" s="11">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B32,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="12">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B32,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>8455</v>
+        <v>8733</v>
       </c>
       <c r="G32" s="13">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="14">
         <f t="shared" si="6"/>
-        <v>8700</v>
+        <v>8978</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="8"/>
-        <v>2.8160919540229885E-2</v>
+        <v>2.7288928491869015E-2</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="16">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B32,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32" s="17">
         <f ca="1">SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B32,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>8700</v>
+        <v>8978</v>
       </c>
       <c r="N32" s="18">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B32,Inventory!$I$2:$I$1000,"Retired")</f>
@@ -7137,44 +7146,44 @@
       </c>
       <c r="E37" s="11">
         <f>COUNTIFS(Inventory!$D$2:$D$1000,B37,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F37" s="12">
         <f>SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B37,Inventory!$H$2:$H$1000,"NO")</f>
-        <v>8227</v>
+        <v>11506</v>
       </c>
       <c r="G37" s="13">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H37" s="14">
         <f t="shared" si="6"/>
-        <v>10854</v>
+        <v>14133</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="7"/>
-        <v>0.42857142857142855</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="8"/>
-        <v>0.24203058780173209</v>
+        <v>0.18587702540154249</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="16">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B37,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37" s="17">
         <f ca="1">SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B37,Inventory!$I$2:$I$1000,"Not Retired")</f>
-        <v>5167</v>
+        <v>6382</v>
       </c>
       <c r="N37" s="18">
         <f ca="1">COUNTIFS(Inventory!$D$2:$D$1000,B37,Inventory!$I$2:$I$1000,"Retired")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O37" s="19">
         <f ca="1">SUMIFS(Inventory!$E$2:$E$1000,Inventory!$D$2:$D$1000,B37,Inventory!$I$2:$I$1000,"Retired")</f>
-        <v>5687</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7245,44 +7254,44 @@
       </c>
       <c r="E39" s="1">
         <f t="shared" si="13"/>
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F39" s="33">
         <f t="shared" si="13"/>
-        <v>117560</v>
+        <v>121117</v>
       </c>
       <c r="G39" s="1">
         <f t="shared" si="13"/>
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H39" s="33">
         <f t="shared" si="13"/>
-        <v>192422</v>
+        <v>195979</v>
       </c>
       <c r="I39" s="34">
         <f t="shared" si="3"/>
-        <v>0.42857142857142855</v>
+        <v>0.42073170731707316</v>
       </c>
       <c r="J39" s="34">
         <f t="shared" si="4"/>
-        <v>0.38905114799763019</v>
+        <v>0.38198990708188124</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="1">
         <f ca="1">SUM(L20:L37)</f>
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M39" s="33">
         <f ca="1">SUM(M20:M37)</f>
-        <v>123747</v>
+        <v>125240</v>
       </c>
       <c r="N39" s="1">
         <f ca="1">SUM(N20:N37)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O39" s="33">
         <f ca="1">SUM(O20:O37)</f>
-        <v>68675</v>
+        <v>70739</v>
       </c>
     </row>
     <row r="40" spans="2:18" ht="11" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -7463,11 +7472,11 @@
       </c>
       <c r="C54" s="39">
         <f>COUNTIF(Inventory!G2:G1000,B54)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" s="40">
         <f>SUMIF(Inventory!G2:G1000,B54,Inventory!E2:E1000)</f>
-        <v>20723</v>
+        <v>22787</v>
       </c>
     </row>
     <row r="55" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7489,11 +7498,11 @@
       </c>
       <c r="C56" s="41">
         <f>COUNTIF(Inventory!G2:G1000,B56)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D56" s="42">
         <f>SUMIF(Inventory!G2:G1000,B56,Inventory!E2:E1000)</f>
-        <v>46250</v>
+        <v>47743</v>
       </c>
       <c r="F56" s="53" t="s">
         <v>41</v>
@@ -7533,11 +7542,11 @@
       </c>
       <c r="C58" s="35">
         <f>SUM(C43:C57)</f>
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D58" s="45">
         <f>SUM(D43:D57)</f>
-        <v>196487</v>
+        <v>200044</v>
       </c>
       <c r="F58" s="21" t="s">
         <v>8</v>
@@ -7551,7 +7560,7 @@
       </c>
       <c r="I58" s="28">
         <f ca="1">+C15</f>
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7560,14 +7569,14 @@
       </c>
       <c r="G59" s="11">
         <f ca="1">+G14</f>
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H59" s="18" t="s">
         <v>13</v>
       </c>
       <c r="I59" s="18">
         <f ca="1">+E15</f>
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="2:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -12796,16 +12805,30 @@
         <f t="shared" si="5"/>
         <v>165</v>
       </c>
-      <c r="B166" s="79"/>
-      <c r="C166" s="61"/>
-      <c r="D166" s="62"/>
-      <c r="E166" s="60"/>
-      <c r="F166" s="60"/>
-      <c r="G166" s="60"/>
-      <c r="H166" s="62"/>
+      <c r="B166" s="79">
+        <v>40886</v>
+      </c>
+      <c r="C166" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="D166" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="E166" s="60">
+        <v>278</v>
+      </c>
+      <c r="F166" s="60">
+        <v>2026</v>
+      </c>
+      <c r="G166" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H166" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I166" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -12813,16 +12836,30 @@
         <f t="shared" si="5"/>
         <v>166</v>
       </c>
-      <c r="B167" s="79"/>
-      <c r="C167" s="61"/>
-      <c r="D167" s="62"/>
-      <c r="E167" s="60"/>
-      <c r="F167" s="60"/>
-      <c r="G167" s="60"/>
-      <c r="H167" s="62"/>
+      <c r="B167" s="79">
+        <v>71438</v>
+      </c>
+      <c r="C167" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="D167" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E167" s="60">
+        <v>1215</v>
+      </c>
+      <c r="F167" s="60">
+        <v>2024</v>
+      </c>
+      <c r="G167" s="60">
+        <v>2026</v>
+      </c>
+      <c r="H167" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I167" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Not Retired</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -12830,16 +12867,30 @@
         <f t="shared" si="5"/>
         <v>167</v>
       </c>
-      <c r="B168" s="79"/>
-      <c r="C168" s="61"/>
-      <c r="D168" s="62"/>
-      <c r="E168" s="60"/>
-      <c r="F168" s="60"/>
-      <c r="G168" s="60"/>
-      <c r="H168" s="62"/>
+      <c r="B168" s="79">
+        <v>71395</v>
+      </c>
+      <c r="C168" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="D168" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168" s="60">
+        <v>2064</v>
+      </c>
+      <c r="F168" s="60">
+        <v>2021</v>
+      </c>
+      <c r="G168" s="60">
+        <v>2024</v>
+      </c>
+      <c r="H168" s="62" t="s">
+        <v>53</v>
+      </c>
       <c r="I168" s="60" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>Retired</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
